--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,6 +872,4448 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132034144</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>695495</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7036285</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132014040</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80246</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>392</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>695319</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7036604</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132014573</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91824</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>695342</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7036654</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132034131</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>695355</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7036639</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132034114</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>695307</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7036500</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132034129</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80277</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>695341</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7036636</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132034128</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56475</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>695583</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7035966</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132034124</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>695363</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7036339</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132034122</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>695347</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7036357</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132034110</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91803</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>695453</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7036611</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132034126</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>695417</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7036333</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132034120</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>695450</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7036585</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132034130</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80373</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>695359</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7036639</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132034132</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80373</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>695353</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7036644</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lunglav på fyra närliggande Aspar</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132034142</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>695378</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7036337</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132034139</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>695472</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7036445</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132034125</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>695395</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7036336</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132034113</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91803</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>695344</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7036394</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132012638</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91803</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>695461</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7036590</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132034137</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>695380</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7036661</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132034117</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>695633</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7036036</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132034115</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>695321</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7036547</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132034121</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>695332</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7036447</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132034118</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58065</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>695490</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7036280</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132034127</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56475</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>695353</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7036635</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132034140</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>695449</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7036505</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132034141</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>695346</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7036396</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132013817</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>695302</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7036682</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132034109</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91803</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>695562</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7036322</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132034116</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>695468</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7036290</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132013416</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>695342</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7036759</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132012907</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91803</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>695475</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7036617</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132014471</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80246</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>392</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>695346</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7036647</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132014637</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80246</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>392</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>695362</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7036633</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132011688</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>695558</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7036477</v>
+      </c>
+      <c r="S38" t="n">
+        <v>141</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132034111</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91803</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>695315</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7036513</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132034138</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>695488</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7036361</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132034143</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>695430</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7036304</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132012332</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91840</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>695536</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7036574</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132006284</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57094</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>695748</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7036138</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132034119</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58065</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>695537</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7036151</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132034112</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91803</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>695306</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7036498</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132034133</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80373</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>695337</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7036645</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -1076,48 +1076,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132014573</v>
+        <v>132034131</v>
       </c>
       <c r="B6" t="n">
-        <v>91824</v>
+        <v>80373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695342</v>
+        <v>695355</v>
       </c>
       <c r="R6" t="n">
-        <v>7036654</v>
+        <v>7036639</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1155,28 +1158,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132034131</v>
+        <v>132034114</v>
       </c>
       <c r="B7" t="n">
-        <v>80373</v>
+        <v>91840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,37 +1203,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695355</v>
+        <v>695307</v>
       </c>
       <c r="R7" t="n">
-        <v>7036639</v>
+        <v>7036500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,24 +1271,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1289,48 +1289,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034114</v>
+        <v>132014573</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695307</v>
+        <v>695342</v>
       </c>
       <c r="R8" t="n">
-        <v>7036500</v>
+        <v>7036654</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1374,12 +1374,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2762,48 +2762,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132012638</v>
+        <v>132034137</v>
       </c>
       <c r="B22" t="n">
-        <v>91803</v>
+        <v>79268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695461</v>
+        <v>695380</v>
       </c>
       <c r="R22" t="n">
-        <v>7036590</v>
+        <v>7036661</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2847,22 +2847,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132034137</v>
+        <v>132034117</v>
       </c>
       <c r="B23" t="n">
-        <v>79268</v>
+        <v>57906</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2870,34 +2870,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695380</v>
+        <v>695633</v>
       </c>
       <c r="R23" t="n">
-        <v>7036661</v>
+        <v>7036036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,6 +2934,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,7 +2965,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132034117</v>
+        <v>132034115</v>
       </c>
       <c r="B24" t="n">
         <v>57906</v>
@@ -2995,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695633</v>
+        <v>695321</v>
       </c>
       <c r="R24" t="n">
-        <v>7036036</v>
+        <v>7036547</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3035,7 +3044,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack på två granar</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3062,52 +3071,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132034115</v>
+        <v>132012638</v>
       </c>
       <c r="B25" t="n">
-        <v>57906</v>
+        <v>91803</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695321</v>
+        <v>695461</v>
       </c>
       <c r="R25" t="n">
-        <v>7036547</v>
+        <v>7036590</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3137,11 +3142,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3156,12 +3156,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132012306</v>
       </c>
       <c r="B2" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132007310</v>
       </c>
       <c r="B3" t="n">
-        <v>57085</v>
+        <v>57086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132034144</v>
       </c>
       <c r="B4" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>132014040</v>
       </c>
       <c r="B5" t="n">
-        <v>80246</v>
+        <v>80247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132034131</v>
+        <v>132034114</v>
       </c>
       <c r="B6" t="n">
-        <v>80373</v>
+        <v>91841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,37 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695355</v>
+        <v>695307</v>
       </c>
       <c r="R6" t="n">
-        <v>7036639</v>
+        <v>7036500</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,24 +1155,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1192,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132034114</v>
+        <v>132034131</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>80374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,34 +1184,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695307</v>
+        <v>695355</v>
       </c>
       <c r="R7" t="n">
-        <v>7036500</v>
+        <v>7036639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,8 +1255,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1292,7 +1292,7 @@
         <v>132014573</v>
       </c>
       <c r="B8" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>132034129</v>
       </c>
       <c r="B9" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>132034128</v>
       </c>
       <c r="B10" t="n">
-        <v>56475</v>
+        <v>56476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>132034124</v>
       </c>
       <c r="B11" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,53 +1709,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132034122</v>
+        <v>132034110</v>
       </c>
       <c r="B12" t="n">
-        <v>57903</v>
+        <v>91804</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695347</v>
+        <v>695453</v>
       </c>
       <c r="R12" t="n">
-        <v>7036357</v>
+        <v>7036611</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,45 +1806,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034110</v>
+        <v>132034122</v>
       </c>
       <c r="B13" t="n">
-        <v>91803</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695453</v>
+        <v>695347</v>
       </c>
       <c r="R13" t="n">
-        <v>7036611</v>
+        <v>7036357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1914,7 @@
         <v>132034126</v>
       </c>
       <c r="B14" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132034120</v>
+        <v>132034130</v>
       </c>
       <c r="B15" t="n">
-        <v>57903</v>
+        <v>80374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,31 +2027,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2059,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695450</v>
+        <v>695359</v>
       </c>
       <c r="R15" t="n">
-        <v>7036585</v>
+        <v>7036639</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,8 +2098,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2121,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132034130</v>
+        <v>132034120</v>
       </c>
       <c r="B16" t="n">
-        <v>80373</v>
+        <v>57904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,26 +2143,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2159,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695359</v>
+        <v>695450</v>
       </c>
       <c r="R16" t="n">
-        <v>7036639</v>
+        <v>7036585</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,24 +2219,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2240,7 +2240,7 @@
         <v>132034132</v>
       </c>
       <c r="B17" t="n">
-        <v>80373</v>
+        <v>80374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034142</v>
+        <v>132034139</v>
       </c>
       <c r="B18" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,16 +2387,23 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695378</v>
+        <v>695472</v>
       </c>
       <c r="R18" t="n">
-        <v>7036337</v>
+        <v>7036445</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,6 +2444,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2455,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034139</v>
+        <v>132034142</v>
       </c>
       <c r="B19" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,23 +2492,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695472</v>
+        <v>695378</v>
       </c>
       <c r="R19" t="n">
-        <v>7036445</v>
+        <v>7036337</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,7 +2542,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2560,53 +2560,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034125</v>
+        <v>132034113</v>
       </c>
       <c r="B20" t="n">
-        <v>57903</v>
+        <v>91804</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695395</v>
+        <v>695344</v>
       </c>
       <c r="R20" t="n">
-        <v>7036336</v>
+        <v>7036394</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,45 +2657,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034113</v>
+        <v>132034125</v>
       </c>
       <c r="B21" t="n">
-        <v>91803</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695344</v>
+        <v>695395</v>
       </c>
       <c r="R21" t="n">
-        <v>7036394</v>
+        <v>7036336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,48 +2762,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132034137</v>
+        <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>79268</v>
+        <v>91804</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695380</v>
+        <v>695461</v>
       </c>
       <c r="R22" t="n">
-        <v>7036661</v>
+        <v>7036590</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2847,22 +2847,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132034117</v>
+        <v>132034137</v>
       </c>
       <c r="B23" t="n">
-        <v>57906</v>
+        <v>79269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2870,38 +2870,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695633</v>
+        <v>695380</v>
       </c>
       <c r="R23" t="n">
-        <v>7036036</v>
+        <v>7036661</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,11 +2930,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2968,7 +2959,7 @@
         <v>132034115</v>
       </c>
       <c r="B24" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,48 +3062,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132012638</v>
+        <v>132034117</v>
       </c>
       <c r="B25" t="n">
-        <v>91803</v>
+        <v>57907</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695461</v>
+        <v>695633</v>
       </c>
       <c r="R25" t="n">
-        <v>7036590</v>
+        <v>7036036</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3142,6 +3137,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3156,12 +3156,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
         <v>132034121</v>
       </c>
       <c r="B26" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,10 +3273,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034118</v>
+        <v>132034140</v>
       </c>
       <c r="B27" t="n">
-        <v>58065</v>
+        <v>79269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,42 +3284,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695490</v>
+        <v>695449</v>
       </c>
       <c r="R27" t="n">
-        <v>7036280</v>
+        <v>7036505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3349,19 +3341,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3388,10 +3370,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034127</v>
+        <v>132034141</v>
       </c>
       <c r="B28" t="n">
-        <v>56475</v>
+        <v>79269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3423,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695353</v>
+        <v>695346</v>
       </c>
       <c r="R28" t="n">
-        <v>7036635</v>
+        <v>7036396</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034140</v>
+        <v>132034118</v>
       </c>
       <c r="B29" t="n">
-        <v>79268</v>
+        <v>58066</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3496,34 +3478,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695449</v>
+        <v>695490</v>
       </c>
       <c r="R29" t="n">
-        <v>7036505</v>
+        <v>7036280</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,9 +3543,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,10 +3582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132034141</v>
+        <v>132034127</v>
       </c>
       <c r="B30" t="n">
-        <v>79268</v>
+        <v>56476</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,21 +3593,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695346</v>
+        <v>695353</v>
       </c>
       <c r="R30" t="n">
-        <v>7036396</v>
+        <v>7036635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,48 +3679,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132013817</v>
+        <v>132034109</v>
       </c>
       <c r="B31" t="n">
-        <v>79268</v>
+        <v>91804</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695302</v>
+        <v>695562</v>
       </c>
       <c r="R31" t="n">
-        <v>7036682</v>
+        <v>7036322</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3764,60 +3764,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132034109</v>
+        <v>132013817</v>
       </c>
       <c r="B32" t="n">
-        <v>91803</v>
+        <v>79269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695562</v>
+        <v>695302</v>
       </c>
       <c r="R32" t="n">
-        <v>7036322</v>
+        <v>7036682</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3876,7 +3876,7 @@
         <v>132034116</v>
       </c>
       <c r="B33" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>132013416</v>
       </c>
       <c r="B34" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>132012907</v>
       </c>
       <c r="B35" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4182,51 +4182,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132014471</v>
+        <v>132011688</v>
       </c>
       <c r="B36" t="n">
-        <v>80246</v>
+        <v>91841</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695346</v>
+        <v>695558</v>
       </c>
       <c r="R36" t="n">
-        <v>7036647</v>
+        <v>7036477</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4264,7 +4261,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4283,10 +4279,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132014637</v>
+        <v>132014471</v>
       </c>
       <c r="B37" t="n">
-        <v>80246</v>
+        <v>80247</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4321,10 +4317,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695362</v>
+        <v>695346</v>
       </c>
       <c r="R37" t="n">
-        <v>7036633</v>
+        <v>7036647</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4384,48 +4380,51 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132011688</v>
+        <v>132014637</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>80247</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695558</v>
+        <v>695362</v>
       </c>
       <c r="R38" t="n">
-        <v>7036477</v>
+        <v>7036633</v>
       </c>
       <c r="S38" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4463,6 +4462,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4481,48 +4481,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132034111</v>
+        <v>132012332</v>
       </c>
       <c r="B39" t="n">
-        <v>91803</v>
+        <v>91841</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695315</v>
+        <v>695536</v>
       </c>
       <c r="R39" t="n">
-        <v>7036513</v>
+        <v>7036574</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4566,12 +4566,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
         <v>132034138</v>
       </c>
       <c r="B40" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132034143</v>
+        <v>132034111</v>
       </c>
       <c r="B41" t="n">
-        <v>79268</v>
+        <v>91804</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695430</v>
+        <v>695315</v>
       </c>
       <c r="R41" t="n">
-        <v>7036304</v>
+        <v>7036513</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132012332</v>
+        <v>132034143</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>79269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,37 +4792,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695536</v>
+        <v>695430</v>
       </c>
       <c r="R42" t="n">
-        <v>7036574</v>
+        <v>7036304</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4881,7 +4881,7 @@
         <v>132006284</v>
       </c>
       <c r="B43" t="n">
-        <v>57094</v>
+        <v>57095</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>132034119</v>
       </c>
       <c r="B44" t="n">
-        <v>58065</v>
+        <v>58066</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>132034112</v>
       </c>
       <c r="B45" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>132034133</v>
       </c>
       <c r="B46" t="n">
-        <v>80373</v>
+        <v>80374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132012306</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132007310</v>
       </c>
       <c r="B3" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132034144</v>
+        <v>132014040</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>80252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,17 +908,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>695495</v>
+        <v>695319</v>
       </c>
       <c r="R4" t="n">
-        <v>7036285</v>
+        <v>7036604</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,44 +963,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132014040</v>
+        <v>132034144</v>
       </c>
       <c r="B5" t="n">
-        <v>80247</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,17 +1009,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695319</v>
+        <v>695495</v>
       </c>
       <c r="R5" t="n">
-        <v>7036604</v>
+        <v>7036285</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,12 +1064,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
         <v>132034114</v>
       </c>
       <c r="B6" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>132034131</v>
       </c>
       <c r="B7" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>132014573</v>
       </c>
       <c r="B8" t="n">
-        <v>91825</v>
+        <v>91830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>132034129</v>
       </c>
       <c r="B9" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>132034128</v>
       </c>
       <c r="B10" t="n">
-        <v>56476</v>
+        <v>56481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>132034124</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132034110</v>
       </c>
       <c r="B12" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>132034122</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>132034126</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>132034130</v>
       </c>
       <c r="B15" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>132034120</v>
       </c>
       <c r="B16" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>132034132</v>
       </c>
       <c r="B17" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>132034139</v>
       </c>
       <c r="B18" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>132034142</v>
       </c>
       <c r="B19" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>132034113</v>
       </c>
       <c r="B20" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>132034125</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>132034137</v>
       </c>
       <c r="B23" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>132034115</v>
       </c>
       <c r="B24" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>132034117</v>
       </c>
       <c r="B25" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132034121</v>
+        <v>132034140</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,42 +3179,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695332</v>
+        <v>695449</v>
       </c>
       <c r="R26" t="n">
-        <v>7036447</v>
+        <v>7036505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3273,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034140</v>
+        <v>132034141</v>
       </c>
       <c r="B27" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3308,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695449</v>
+        <v>695346</v>
       </c>
       <c r="R27" t="n">
-        <v>7036505</v>
+        <v>7036396</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034141</v>
+        <v>132034121</v>
       </c>
       <c r="B28" t="n">
-        <v>79269</v>
+        <v>57909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,34 +3373,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695346</v>
+        <v>695332</v>
       </c>
       <c r="R28" t="n">
-        <v>7036396</v>
+        <v>7036447</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
         <v>132034118</v>
       </c>
       <c r="B29" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>132034127</v>
       </c>
       <c r="B30" t="n">
-        <v>56476</v>
+        <v>56481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,48 +3679,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132034109</v>
+        <v>132013817</v>
       </c>
       <c r="B31" t="n">
-        <v>91804</v>
+        <v>79274</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695562</v>
+        <v>695302</v>
       </c>
       <c r="R31" t="n">
-        <v>7036322</v>
+        <v>7036682</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3764,22 +3764,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132013817</v>
+        <v>132034116</v>
       </c>
       <c r="B32" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3787,37 +3787,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695302</v>
+        <v>695468</v>
       </c>
       <c r="R32" t="n">
-        <v>7036682</v>
+        <v>7036290</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,6 +3847,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3861,44 +3866,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132034116</v>
+        <v>132034109</v>
       </c>
       <c r="B33" t="n">
-        <v>57907</v>
+        <v>91809</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3908,10 +3913,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695468</v>
+        <v>695562</v>
       </c>
       <c r="R33" t="n">
-        <v>7036290</v>
+        <v>7036322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,11 +3949,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3978,7 +3978,7 @@
         <v>132013416</v>
       </c>
       <c r="B34" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>132012907</v>
       </c>
       <c r="B35" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>132011688</v>
       </c>
       <c r="B36" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>132014471</v>
       </c>
       <c r="B37" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>132014637</v>
       </c>
       <c r="B38" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132012332</v>
+        <v>132034138</v>
       </c>
       <c r="B39" t="n">
-        <v>91841</v>
+        <v>79274</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,37 +4492,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695536</v>
+        <v>695488</v>
       </c>
       <c r="R39" t="n">
-        <v>7036574</v>
+        <v>7036361</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4554,72 +4557,75 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132034138</v>
+        <v>132034111</v>
       </c>
       <c r="B40" t="n">
-        <v>79269</v>
+        <v>91809</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695488</v>
+        <v>695315</v>
       </c>
       <c r="R40" t="n">
-        <v>7036361</v>
+        <v>7036513</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4654,18 +4660,12 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132034111</v>
+        <v>132034143</v>
       </c>
       <c r="B41" t="n">
-        <v>91804</v>
+        <v>79274</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695315</v>
+        <v>695430</v>
       </c>
       <c r="R41" t="n">
-        <v>7036513</v>
+        <v>7036304</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,48 +4781,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132034143</v>
+        <v>132006284</v>
       </c>
       <c r="B42" t="n">
-        <v>79269</v>
+        <v>57100</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695430</v>
+        <v>695748</v>
       </c>
       <c r="R42" t="n">
-        <v>7036304</v>
+        <v>7036138</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4866,62 +4871,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132006284</v>
+        <v>132012332</v>
       </c>
       <c r="B43" t="n">
-        <v>57095</v>
+        <v>91846</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695748</v>
+        <v>695536</v>
       </c>
       <c r="R43" t="n">
-        <v>7036138</v>
+        <v>7036574</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>132034119</v>
       </c>
       <c r="B44" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>132034112</v>
       </c>
       <c r="B45" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>132034133</v>
       </c>
       <c r="B46" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132012306</v>
       </c>
       <c r="B2" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132007310</v>
       </c>
       <c r="B3" t="n">
-        <v>57091</v>
+        <v>57093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132014040</v>
       </c>
       <c r="B4" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>132034144</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132034114</v>
+        <v>132034131</v>
       </c>
       <c r="B6" t="n">
-        <v>91846</v>
+        <v>80381</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695307</v>
+        <v>695355</v>
       </c>
       <c r="R6" t="n">
-        <v>7036500</v>
+        <v>7036639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,8 +1158,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1173,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132034131</v>
+        <v>132034114</v>
       </c>
       <c r="B7" t="n">
-        <v>80379</v>
+        <v>91848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,37 +1203,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695355</v>
+        <v>695307</v>
       </c>
       <c r="R7" t="n">
-        <v>7036639</v>
+        <v>7036500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,24 +1271,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1292,7 +1292,7 @@
         <v>132014573</v>
       </c>
       <c r="B8" t="n">
-        <v>91830</v>
+        <v>91832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>132034129</v>
       </c>
       <c r="B9" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>132034128</v>
       </c>
       <c r="B10" t="n">
-        <v>56481</v>
+        <v>56483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>132034124</v>
       </c>
       <c r="B11" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132034110</v>
       </c>
       <c r="B12" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>132034122</v>
       </c>
       <c r="B13" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>132034126</v>
       </c>
       <c r="B14" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>132034130</v>
       </c>
       <c r="B15" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>132034120</v>
       </c>
       <c r="B16" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>132034132</v>
       </c>
       <c r="B17" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,52 +2358,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034139</v>
+        <v>132034113</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>91811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695472</v>
+        <v>695344</v>
       </c>
       <c r="R18" t="n">
-        <v>7036445</v>
+        <v>7036394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,7 +2437,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2463,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034142</v>
+        <v>132034125</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,34 +2466,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695378</v>
+        <v>695395</v>
       </c>
       <c r="R19" t="n">
-        <v>7036337</v>
+        <v>7036336</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,45 +2560,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034113</v>
+        <v>132034139</v>
       </c>
       <c r="B20" t="n">
-        <v>91809</v>
+        <v>79276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695344</v>
+        <v>695472</v>
       </c>
       <c r="R20" t="n">
-        <v>7036394</v>
+        <v>7036445</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,6 +2646,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2657,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034125</v>
+        <v>132034142</v>
       </c>
       <c r="B21" t="n">
-        <v>57909</v>
+        <v>79276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,42 +2676,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695395</v>
+        <v>695378</v>
       </c>
       <c r="R21" t="n">
-        <v>7036336</v>
+        <v>7036337</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
         <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>132034137</v>
       </c>
       <c r="B23" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>132034115</v>
       </c>
       <c r="B24" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>132034117</v>
       </c>
       <c r="B25" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>132034140</v>
       </c>
       <c r="B26" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>132034141</v>
       </c>
       <c r="B27" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>132034121</v>
       </c>
       <c r="B28" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>132034118</v>
       </c>
       <c r="B29" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>132034127</v>
       </c>
       <c r="B30" t="n">
-        <v>56481</v>
+        <v>56483</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,48 +3679,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132013817</v>
+        <v>132034109</v>
       </c>
       <c r="B31" t="n">
-        <v>79274</v>
+        <v>91811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695302</v>
+        <v>695562</v>
       </c>
       <c r="R31" t="n">
-        <v>7036682</v>
+        <v>7036322</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3764,22 +3764,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132034116</v>
+        <v>132013817</v>
       </c>
       <c r="B32" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3787,37 +3787,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695468</v>
+        <v>695302</v>
       </c>
       <c r="R32" t="n">
-        <v>7036290</v>
+        <v>7036682</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,11 +3847,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,44 +3861,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132034109</v>
+        <v>132034116</v>
       </c>
       <c r="B33" t="n">
-        <v>91809</v>
+        <v>57914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3913,10 +3908,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695562</v>
+        <v>695468</v>
       </c>
       <c r="R33" t="n">
-        <v>7036322</v>
+        <v>7036290</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,6 +3944,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3978,7 +3978,7 @@
         <v>132013416</v>
       </c>
       <c r="B34" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,45 +4085,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132012907</v>
+        <v>132014637</v>
       </c>
       <c r="B35" t="n">
-        <v>91809</v>
+        <v>80254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695475</v>
+        <v>695362</v>
       </c>
       <c r="R35" t="n">
-        <v>7036617</v>
+        <v>7036633</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4164,6 +4167,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4182,48 +4186,51 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132011688</v>
+        <v>132014471</v>
       </c>
       <c r="B36" t="n">
-        <v>91846</v>
+        <v>80254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695558</v>
+        <v>695346</v>
       </c>
       <c r="R36" t="n">
-        <v>7036477</v>
+        <v>7036647</v>
       </c>
       <c r="S36" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4261,6 +4268,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4279,51 +4287,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132014471</v>
+        <v>132011688</v>
       </c>
       <c r="B37" t="n">
-        <v>80252</v>
+        <v>91848</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695346</v>
+        <v>695558</v>
       </c>
       <c r="R37" t="n">
-        <v>7036647</v>
+        <v>7036477</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4361,7 +4366,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4380,48 +4384,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132014637</v>
+        <v>132012907</v>
       </c>
       <c r="B38" t="n">
-        <v>80252</v>
+        <v>91811</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695362</v>
+        <v>695475</v>
       </c>
       <c r="R38" t="n">
-        <v>7036633</v>
+        <v>7036617</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4462,7 +4463,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4481,48 +4481,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132034138</v>
+        <v>132034111</v>
       </c>
       <c r="B39" t="n">
-        <v>79274</v>
+        <v>91811</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695488</v>
+        <v>695315</v>
       </c>
       <c r="R39" t="n">
-        <v>7036361</v>
+        <v>7036513</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,18 +4554,12 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4587,48 +4578,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132034111</v>
+        <v>132012332</v>
       </c>
       <c r="B40" t="n">
-        <v>91809</v>
+        <v>91848</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695315</v>
+        <v>695536</v>
       </c>
       <c r="R40" t="n">
-        <v>7036513</v>
+        <v>7036574</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4672,60 +4663,65 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132034143</v>
+        <v>132006284</v>
       </c>
       <c r="B41" t="n">
-        <v>79274</v>
+        <v>57102</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695430</v>
+        <v>695748</v>
       </c>
       <c r="R41" t="n">
-        <v>7036304</v>
+        <v>7036138</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4769,65 +4765,63 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132006284</v>
+        <v>132034138</v>
       </c>
       <c r="B42" t="n">
-        <v>57100</v>
+        <v>79276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695748</v>
+        <v>695488</v>
       </c>
       <c r="R42" t="n">
-        <v>7036138</v>
+        <v>7036361</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4859,34 +4853,40 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132012332</v>
+        <v>132034143</v>
       </c>
       <c r="B43" t="n">
-        <v>91846</v>
+        <v>79276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4894,37 +4894,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695536</v>
+        <v>695430</v>
       </c>
       <c r="R43" t="n">
-        <v>7036574</v>
+        <v>7036304</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4968,12 +4968,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4983,7 +4983,7 @@
         <v>132034119</v>
       </c>
       <c r="B44" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>132034112</v>
       </c>
       <c r="B45" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>132034133</v>
       </c>
       <c r="B46" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132034130</v>
+        <v>132034120</v>
       </c>
       <c r="B15" t="n">
-        <v>80381</v>
+        <v>57911</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,26 +2027,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2054,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695359</v>
+        <v>695450</v>
       </c>
       <c r="R15" t="n">
-        <v>7036639</v>
+        <v>7036585</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,24 +2103,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2132,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132034120</v>
+        <v>132034130</v>
       </c>
       <c r="B16" t="n">
-        <v>57911</v>
+        <v>80381</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,31 +2132,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2175,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695450</v>
+        <v>695359</v>
       </c>
       <c r="R16" t="n">
-        <v>7036585</v>
+        <v>7036639</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,8 +2203,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2762,48 +2762,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132012638</v>
+        <v>132034115</v>
       </c>
       <c r="B22" t="n">
-        <v>91811</v>
+        <v>57914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695461</v>
+        <v>695321</v>
       </c>
       <c r="R22" t="n">
-        <v>7036590</v>
+        <v>7036547</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2833,6 +2837,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,22 +2856,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132034137</v>
+        <v>132034117</v>
       </c>
       <c r="B23" t="n">
-        <v>79276</v>
+        <v>57914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2870,34 +2879,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695380</v>
+        <v>695633</v>
       </c>
       <c r="R23" t="n">
-        <v>7036661</v>
+        <v>7036036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,6 +2943,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,52 +2974,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132034115</v>
+        <v>132012638</v>
       </c>
       <c r="B24" t="n">
-        <v>57914</v>
+        <v>91811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695321</v>
+        <v>695461</v>
       </c>
       <c r="R24" t="n">
-        <v>7036547</v>
+        <v>7036590</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3031,11 +3045,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3050,22 +3059,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132034117</v>
+        <v>132034137</v>
       </c>
       <c r="B25" t="n">
-        <v>57914</v>
+        <v>79276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3073,38 +3082,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695633</v>
+        <v>695380</v>
       </c>
       <c r="R25" t="n">
-        <v>7036036</v>
+        <v>7036661</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3137,11 +3142,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3776,10 +3776,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132013817</v>
+        <v>132034116</v>
       </c>
       <c r="B32" t="n">
-        <v>79276</v>
+        <v>57914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3787,37 +3787,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695302</v>
+        <v>695468</v>
       </c>
       <c r="R32" t="n">
-        <v>7036682</v>
+        <v>7036290</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,6 +3847,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3861,22 +3866,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132034116</v>
+        <v>132013817</v>
       </c>
       <c r="B33" t="n">
-        <v>57914</v>
+        <v>79276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3884,37 +3889,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695468</v>
+        <v>695302</v>
       </c>
       <c r="R33" t="n">
-        <v>7036290</v>
+        <v>7036682</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3944,11 +3949,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3963,12 +3963,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132034131</v>
+        <v>132034114</v>
       </c>
       <c r="B6" t="n">
-        <v>80381</v>
+        <v>91848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,37 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695355</v>
+        <v>695307</v>
       </c>
       <c r="R6" t="n">
-        <v>7036639</v>
+        <v>7036500</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,24 +1155,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1192,48 +1173,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132034114</v>
+        <v>132014573</v>
       </c>
       <c r="B7" t="n">
-        <v>91848</v>
+        <v>91832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695307</v>
+        <v>695342</v>
       </c>
       <c r="R7" t="n">
-        <v>7036500</v>
+        <v>7036654</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1277,60 +1258,63 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132014573</v>
+        <v>132034131</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>80381</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695342</v>
+        <v>695355</v>
       </c>
       <c r="R8" t="n">
-        <v>7036654</v>
+        <v>7036639</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,18 +1352,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2358,45 +2358,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034113</v>
+        <v>132034139</v>
       </c>
       <c r="B18" t="n">
-        <v>91811</v>
+        <v>79276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695344</v>
+        <v>695472</v>
       </c>
       <c r="R18" t="n">
-        <v>7036394</v>
+        <v>7036445</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,6 +2444,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2455,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034125</v>
+        <v>132034142</v>
       </c>
       <c r="B19" t="n">
-        <v>57911</v>
+        <v>79276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,42 +2474,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695395</v>
+        <v>695378</v>
       </c>
       <c r="R19" t="n">
-        <v>7036336</v>
+        <v>7036337</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,52 +2560,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034139</v>
+        <v>132034113</v>
       </c>
       <c r="B20" t="n">
-        <v>79276</v>
+        <v>91811</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695472</v>
+        <v>695344</v>
       </c>
       <c r="R20" t="n">
-        <v>7036445</v>
+        <v>7036394</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,7 +2639,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2665,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034142</v>
+        <v>132034125</v>
       </c>
       <c r="B21" t="n">
-        <v>79276</v>
+        <v>57911</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,34 +2668,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695378</v>
+        <v>695395</v>
       </c>
       <c r="R21" t="n">
-        <v>7036337</v>
+        <v>7036336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,52 +2762,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132034115</v>
+        <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>57914</v>
+        <v>91811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695321</v>
+        <v>695461</v>
       </c>
       <c r="R22" t="n">
-        <v>7036547</v>
+        <v>7036590</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2837,11 +2833,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2856,22 +2847,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132034117</v>
+        <v>132034137</v>
       </c>
       <c r="B23" t="n">
-        <v>57914</v>
+        <v>79276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,38 +2870,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695633</v>
+        <v>695380</v>
       </c>
       <c r="R23" t="n">
-        <v>7036036</v>
+        <v>7036661</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,11 +2930,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,48 +2956,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132012638</v>
+        <v>132034115</v>
       </c>
       <c r="B24" t="n">
-        <v>91811</v>
+        <v>57914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695461</v>
+        <v>695321</v>
       </c>
       <c r="R24" t="n">
-        <v>7036590</v>
+        <v>7036547</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3045,6 +3031,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3059,22 +3050,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132034137</v>
+        <v>132034117</v>
       </c>
       <c r="B25" t="n">
-        <v>79276</v>
+        <v>57914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,34 +3073,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695380</v>
+        <v>695633</v>
       </c>
       <c r="R25" t="n">
-        <v>7036661</v>
+        <v>7036036</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3142,6 +3137,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132034140</v>
+        <v>132034118</v>
       </c>
       <c r="B26" t="n">
-        <v>79276</v>
+        <v>58073</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,34 +3179,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695449</v>
+        <v>695490</v>
       </c>
       <c r="R26" t="n">
-        <v>7036505</v>
+        <v>7036280</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3236,9 +3244,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3265,10 +3283,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034141</v>
+        <v>132034127</v>
       </c>
       <c r="B27" t="n">
-        <v>79276</v>
+        <v>56483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3276,21 +3294,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3300,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695346</v>
+        <v>695353</v>
       </c>
       <c r="R27" t="n">
-        <v>7036396</v>
+        <v>7036635</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3362,10 +3380,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034121</v>
+        <v>132034140</v>
       </c>
       <c r="B28" t="n">
-        <v>57911</v>
+        <v>79276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,42 +3391,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695332</v>
+        <v>695449</v>
       </c>
       <c r="R28" t="n">
-        <v>7036447</v>
+        <v>7036505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,10 +3477,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034118</v>
+        <v>132034141</v>
       </c>
       <c r="B29" t="n">
-        <v>58073</v>
+        <v>79276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,42 +3488,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695490</v>
+        <v>695346</v>
       </c>
       <c r="R29" t="n">
-        <v>7036280</v>
+        <v>7036396</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,19 +3545,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,10 +3574,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132034127</v>
+        <v>132034121</v>
       </c>
       <c r="B30" t="n">
-        <v>56483</v>
+        <v>57911</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,34 +3585,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695353</v>
+        <v>695332</v>
       </c>
       <c r="R30" t="n">
-        <v>7036635</v>
+        <v>7036447</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132034116</v>
+        <v>132013817</v>
       </c>
       <c r="B32" t="n">
-        <v>57914</v>
+        <v>79276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3787,37 +3787,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695468</v>
+        <v>695302</v>
       </c>
       <c r="R32" t="n">
-        <v>7036290</v>
+        <v>7036682</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,11 +3847,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,22 +3861,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132013817</v>
+        <v>132034116</v>
       </c>
       <c r="B33" t="n">
-        <v>79276</v>
+        <v>57914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3889,37 +3884,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695302</v>
+        <v>695468</v>
       </c>
       <c r="R33" t="n">
-        <v>7036682</v>
+        <v>7036290</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3949,6 +3944,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3963,12 +3963,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132014637</v>
+        <v>132014471</v>
       </c>
       <c r="B35" t="n">
         <v>80254</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695362</v>
+        <v>695346</v>
       </c>
       <c r="R35" t="n">
-        <v>7036633</v>
+        <v>7036647</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132014471</v>
+        <v>132014637</v>
       </c>
       <c r="B36" t="n">
         <v>80254</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695346</v>
+        <v>695362</v>
       </c>
       <c r="R36" t="n">
-        <v>7036647</v>
+        <v>7036633</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4481,48 +4481,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132034111</v>
+        <v>132012332</v>
       </c>
       <c r="B39" t="n">
-        <v>91811</v>
+        <v>91848</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695315</v>
+        <v>695536</v>
       </c>
       <c r="R39" t="n">
-        <v>7036513</v>
+        <v>7036574</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4566,22 +4566,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132012332</v>
+        <v>132034138</v>
       </c>
       <c r="B40" t="n">
-        <v>91848</v>
+        <v>79276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4589,37 +4589,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695536</v>
+        <v>695488</v>
       </c>
       <c r="R40" t="n">
-        <v>7036574</v>
+        <v>7036361</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4651,34 +4654,40 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132006284</v>
+        <v>132034111</v>
       </c>
       <c r="B41" t="n">
-        <v>57102</v>
+        <v>91811</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4686,42 +4695,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695748</v>
+        <v>695315</v>
       </c>
       <c r="R41" t="n">
-        <v>7036138</v>
+        <v>7036513</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4765,19 +4769,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132034138</v>
+        <v>132034143</v>
       </c>
       <c r="B42" t="n">
         <v>79276</v>
@@ -4806,19 +4810,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695488</v>
+        <v>695430</v>
       </c>
       <c r="R42" t="n">
-        <v>7036361</v>
+        <v>7036304</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4853,18 +4854,12 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4883,48 +4878,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132034143</v>
+        <v>132006284</v>
       </c>
       <c r="B43" t="n">
-        <v>79276</v>
+        <v>57102</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695430</v>
+        <v>695748</v>
       </c>
       <c r="R43" t="n">
-        <v>7036304</v>
+        <v>7036138</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4968,12 +4968,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -2762,48 +2762,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132012638</v>
+        <v>132034137</v>
       </c>
       <c r="B22" t="n">
-        <v>91811</v>
+        <v>79276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695461</v>
+        <v>695380</v>
       </c>
       <c r="R22" t="n">
-        <v>7036590</v>
+        <v>7036661</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2847,60 +2847,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132034137</v>
+        <v>132012638</v>
       </c>
       <c r="B23" t="n">
-        <v>79276</v>
+        <v>91811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695380</v>
+        <v>695461</v>
       </c>
       <c r="R23" t="n">
-        <v>7036661</v>
+        <v>7036590</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2944,12 +2944,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132034118</v>
+        <v>132034121</v>
       </c>
       <c r="B26" t="n">
-        <v>58073</v>
+        <v>57911</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,21 +3179,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3201,7 +3201,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695490</v>
+        <v>695332</v>
       </c>
       <c r="R26" t="n">
-        <v>7036280</v>
+        <v>7036447</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,19 +3244,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3283,10 +3273,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034127</v>
+        <v>132034118</v>
       </c>
       <c r="B27" t="n">
-        <v>56483</v>
+        <v>58073</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,34 +3284,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695353</v>
+        <v>695490</v>
       </c>
       <c r="R27" t="n">
-        <v>7036635</v>
+        <v>7036280</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,9 +3349,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3574,10 +3582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132034121</v>
+        <v>132034127</v>
       </c>
       <c r="B30" t="n">
-        <v>57911</v>
+        <v>56483</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3585,42 +3593,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695332</v>
+        <v>695353</v>
       </c>
       <c r="R30" t="n">
-        <v>7036447</v>
+        <v>7036635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,48 +3679,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132034109</v>
+        <v>132013817</v>
       </c>
       <c r="B31" t="n">
-        <v>91811</v>
+        <v>79276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695562</v>
+        <v>695302</v>
       </c>
       <c r="R31" t="n">
-        <v>7036322</v>
+        <v>7036682</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3764,60 +3764,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132013817</v>
+        <v>132034109</v>
       </c>
       <c r="B32" t="n">
-        <v>79276</v>
+        <v>91811</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695302</v>
+        <v>695562</v>
       </c>
       <c r="R32" t="n">
-        <v>7036682</v>
+        <v>7036322</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132012332</v>
+        <v>132034138</v>
       </c>
       <c r="B39" t="n">
-        <v>91848</v>
+        <v>79276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,37 +4492,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695536</v>
+        <v>695488</v>
       </c>
       <c r="R39" t="n">
-        <v>7036574</v>
+        <v>7036361</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4554,31 +4557,37 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132034138</v>
+        <v>132034143</v>
       </c>
       <c r="B40" t="n">
         <v>79276</v>
@@ -4607,19 +4616,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695488</v>
+        <v>695430</v>
       </c>
       <c r="R40" t="n">
-        <v>7036361</v>
+        <v>7036304</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4654,18 +4660,12 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132034143</v>
+        <v>132012332</v>
       </c>
       <c r="B42" t="n">
-        <v>79276</v>
+        <v>91848</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,37 +4792,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695430</v>
+        <v>695536</v>
       </c>
       <c r="R42" t="n">
-        <v>7036304</v>
+        <v>7036574</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -1709,45 +1709,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132034110</v>
+        <v>132034122</v>
       </c>
       <c r="B12" t="n">
-        <v>91811</v>
+        <v>57911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695453</v>
+        <v>695347</v>
       </c>
       <c r="R12" t="n">
-        <v>7036611</v>
+        <v>7036357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,7 +1814,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034122</v>
+        <v>132034126</v>
       </c>
       <c r="B13" t="n">
         <v>57911</v>
@@ -1839,7 +1847,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1849,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695347</v>
+        <v>695417</v>
       </c>
       <c r="R13" t="n">
-        <v>7036357</v>
+        <v>7036333</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,53 +1919,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034126</v>
+        <v>132034110</v>
       </c>
       <c r="B14" t="n">
-        <v>57911</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695417</v>
+        <v>695453</v>
       </c>
       <c r="R14" t="n">
-        <v>7036333</v>
+        <v>7036611</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132034120</v>
+        <v>132034130</v>
       </c>
       <c r="B15" t="n">
-        <v>57911</v>
+        <v>80381</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,31 +2027,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2059,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695450</v>
+        <v>695359</v>
       </c>
       <c r="R15" t="n">
-        <v>7036585</v>
+        <v>7036639</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,8 +2098,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2121,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132034130</v>
+        <v>132034120</v>
       </c>
       <c r="B16" t="n">
-        <v>80381</v>
+        <v>57911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,26 +2143,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2159,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695359</v>
+        <v>695450</v>
       </c>
       <c r="R16" t="n">
-        <v>7036639</v>
+        <v>7036585</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,24 +2219,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2358,52 +2358,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034139</v>
+        <v>132034113</v>
       </c>
       <c r="B18" t="n">
-        <v>79276</v>
+        <v>91811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695472</v>
+        <v>695344</v>
       </c>
       <c r="R18" t="n">
-        <v>7036445</v>
+        <v>7036394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,7 +2437,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2463,7 +2455,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034142</v>
+        <v>132034139</v>
       </c>
       <c r="B19" t="n">
         <v>79276</v>
@@ -2492,16 +2484,23 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695378</v>
+        <v>695472</v>
       </c>
       <c r="R19" t="n">
-        <v>7036337</v>
+        <v>7036445</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,6 +2541,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2560,32 +2560,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034113</v>
+        <v>132034142</v>
       </c>
       <c r="B20" t="n">
-        <v>91811</v>
+        <v>79276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695344</v>
+        <v>695378</v>
       </c>
       <c r="R20" t="n">
-        <v>7036394</v>
+        <v>7036337</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2762,48 +2762,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132034137</v>
+        <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>79276</v>
+        <v>91811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695380</v>
+        <v>695461</v>
       </c>
       <c r="R22" t="n">
-        <v>7036661</v>
+        <v>7036590</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2847,60 +2847,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132012638</v>
+        <v>132034137</v>
       </c>
       <c r="B23" t="n">
-        <v>91811</v>
+        <v>79276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695461</v>
+        <v>695380</v>
       </c>
       <c r="R23" t="n">
-        <v>7036590</v>
+        <v>7036661</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2944,12 +2944,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034118</v>
+        <v>132034140</v>
       </c>
       <c r="B27" t="n">
-        <v>58073</v>
+        <v>79276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,42 +3284,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695490</v>
+        <v>695449</v>
       </c>
       <c r="R27" t="n">
-        <v>7036280</v>
+        <v>7036505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3349,19 +3341,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3388,7 +3370,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034140</v>
+        <v>132034141</v>
       </c>
       <c r="B28" t="n">
         <v>79276</v>
@@ -3423,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695449</v>
+        <v>695346</v>
       </c>
       <c r="R28" t="n">
-        <v>7036505</v>
+        <v>7036396</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034141</v>
+        <v>132034118</v>
       </c>
       <c r="B29" t="n">
-        <v>79276</v>
+        <v>58073</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3496,34 +3478,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695346</v>
+        <v>695490</v>
       </c>
       <c r="R29" t="n">
-        <v>7036396</v>
+        <v>7036280</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,9 +3543,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3776,32 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132034109</v>
+        <v>132034116</v>
       </c>
       <c r="B32" t="n">
-        <v>91811</v>
+        <v>57914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695562</v>
+        <v>695468</v>
       </c>
       <c r="R32" t="n">
-        <v>7036322</v>
+        <v>7036290</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,6 +3847,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3873,32 +3878,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132034116</v>
+        <v>132034109</v>
       </c>
       <c r="B33" t="n">
-        <v>57914</v>
+        <v>91811</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3908,10 +3913,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695468</v>
+        <v>695562</v>
       </c>
       <c r="R33" t="n">
-        <v>7036290</v>
+        <v>7036322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,11 +3949,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4085,51 +4085,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132014471</v>
+        <v>132011688</v>
       </c>
       <c r="B35" t="n">
-        <v>80254</v>
+        <v>91848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695346</v>
+        <v>695558</v>
       </c>
       <c r="R35" t="n">
-        <v>7036647</v>
+        <v>7036477</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4167,7 +4164,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4186,48 +4182,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132014637</v>
+        <v>132012907</v>
       </c>
       <c r="B36" t="n">
-        <v>80254</v>
+        <v>91811</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695362</v>
+        <v>695475</v>
       </c>
       <c r="R36" t="n">
-        <v>7036633</v>
+        <v>7036617</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4268,7 +4261,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4287,48 +4279,51 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132011688</v>
+        <v>132014471</v>
       </c>
       <c r="B37" t="n">
-        <v>91848</v>
+        <v>80254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695558</v>
+        <v>695346</v>
       </c>
       <c r="R37" t="n">
-        <v>7036477</v>
+        <v>7036647</v>
       </c>
       <c r="S37" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4366,6 +4361,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4384,45 +4380,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132012907</v>
+        <v>132014637</v>
       </c>
       <c r="B38" t="n">
-        <v>91811</v>
+        <v>80254</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695475</v>
+        <v>695362</v>
       </c>
       <c r="R38" t="n">
-        <v>7036617</v>
+        <v>7036633</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4463,6 +4462,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -1709,53 +1709,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132034122</v>
+        <v>132034110</v>
       </c>
       <c r="B12" t="n">
-        <v>57911</v>
+        <v>91811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695347</v>
+        <v>695453</v>
       </c>
       <c r="R12" t="n">
-        <v>7036357</v>
+        <v>7036611</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034126</v>
+        <v>132034122</v>
       </c>
       <c r="B13" t="n">
         <v>57911</v>
@@ -1847,7 +1839,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1857,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695417</v>
+        <v>695347</v>
       </c>
       <c r="R13" t="n">
-        <v>7036333</v>
+        <v>7036357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,45 +1911,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034110</v>
+        <v>132034126</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>57911</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695453</v>
+        <v>695417</v>
       </c>
       <c r="R14" t="n">
-        <v>7036611</v>
+        <v>7036333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2762,48 +2762,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132012638</v>
+        <v>132034137</v>
       </c>
       <c r="B22" t="n">
-        <v>91811</v>
+        <v>79276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695461</v>
+        <v>695380</v>
       </c>
       <c r="R22" t="n">
-        <v>7036590</v>
+        <v>7036661</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2847,60 +2847,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132034137</v>
+        <v>132012638</v>
       </c>
       <c r="B23" t="n">
-        <v>79276</v>
+        <v>91811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695380</v>
+        <v>695461</v>
       </c>
       <c r="R23" t="n">
-        <v>7036661</v>
+        <v>7036590</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2944,12 +2944,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132014040</v>
+        <v>132034144</v>
       </c>
       <c r="B4" t="n">
-        <v>80254</v>
+        <v>79276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,17 +908,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>695319</v>
+        <v>695495</v>
       </c>
       <c r="R4" t="n">
-        <v>7036604</v>
+        <v>7036285</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,44 +963,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132034144</v>
+        <v>132014040</v>
       </c>
       <c r="B5" t="n">
-        <v>79276</v>
+        <v>80254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,17 +1009,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695495</v>
+        <v>695319</v>
       </c>
       <c r="R5" t="n">
-        <v>7036285</v>
+        <v>7036604</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,12 +1064,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1173,48 +1173,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132014573</v>
+        <v>132034131</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>80381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695342</v>
+        <v>695355</v>
       </c>
       <c r="R7" t="n">
-        <v>7036654</v>
+        <v>7036639</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1252,69 +1255,82 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034131</v>
+        <v>132014573</v>
       </c>
       <c r="B8" t="n">
-        <v>80381</v>
+        <v>91832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695355</v>
+        <v>695342</v>
       </c>
       <c r="R8" t="n">
-        <v>7036639</v>
+        <v>7036654</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,34 +1368,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2358,45 +2358,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034113</v>
+        <v>132034125</v>
       </c>
       <c r="B18" t="n">
-        <v>91811</v>
+        <v>57911</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695344</v>
+        <v>695395</v>
       </c>
       <c r="R18" t="n">
-        <v>7036394</v>
+        <v>7036336</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,53 +2665,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034125</v>
+        <v>132034113</v>
       </c>
       <c r="B21" t="n">
-        <v>57911</v>
+        <v>91811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695395</v>
+        <v>695344</v>
       </c>
       <c r="R21" t="n">
-        <v>7036336</v>
+        <v>7036394</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,48 +2762,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132034137</v>
+        <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>79276</v>
+        <v>91811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695380</v>
+        <v>695461</v>
       </c>
       <c r="R22" t="n">
-        <v>7036661</v>
+        <v>7036590</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2847,60 +2847,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132012638</v>
+        <v>132034137</v>
       </c>
       <c r="B23" t="n">
-        <v>91811</v>
+        <v>79276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695461</v>
+        <v>695380</v>
       </c>
       <c r="R23" t="n">
-        <v>7036590</v>
+        <v>7036661</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2944,12 +2944,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132034121</v>
+        <v>132034140</v>
       </c>
       <c r="B26" t="n">
-        <v>57911</v>
+        <v>79276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,42 +3179,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695332</v>
+        <v>695449</v>
       </c>
       <c r="R26" t="n">
-        <v>7036447</v>
+        <v>7036505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3273,7 +3265,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034140</v>
+        <v>132034141</v>
       </c>
       <c r="B27" t="n">
         <v>79276</v>
@@ -3308,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695449</v>
+        <v>695346</v>
       </c>
       <c r="R27" t="n">
-        <v>7036505</v>
+        <v>7036396</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034141</v>
+        <v>132034121</v>
       </c>
       <c r="B28" t="n">
-        <v>79276</v>
+        <v>57911</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,34 +3373,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695346</v>
+        <v>695332</v>
       </c>
       <c r="R28" t="n">
-        <v>7036396</v>
+        <v>7036447</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,48 +3679,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132013817</v>
+        <v>132034109</v>
       </c>
       <c r="B31" t="n">
-        <v>79276</v>
+        <v>91811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695302</v>
+        <v>695562</v>
       </c>
       <c r="R31" t="n">
-        <v>7036682</v>
+        <v>7036322</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3764,22 +3764,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132034116</v>
+        <v>132013817</v>
       </c>
       <c r="B32" t="n">
-        <v>57914</v>
+        <v>79276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3787,37 +3787,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695468</v>
+        <v>695302</v>
       </c>
       <c r="R32" t="n">
-        <v>7036290</v>
+        <v>7036682</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,11 +3847,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,44 +3861,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132034109</v>
+        <v>132034116</v>
       </c>
       <c r="B33" t="n">
-        <v>91811</v>
+        <v>57914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3913,10 +3908,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695562</v>
+        <v>695468</v>
       </c>
       <c r="R33" t="n">
-        <v>7036322</v>
+        <v>7036290</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,6 +3944,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4085,32 +4085,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132011688</v>
+        <v>132012907</v>
       </c>
       <c r="B35" t="n">
-        <v>91848</v>
+        <v>91811</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4120,13 +4120,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695558</v>
+        <v>695475</v>
       </c>
       <c r="R35" t="n">
-        <v>7036477</v>
+        <v>7036617</v>
       </c>
       <c r="S35" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132012907</v>
+        <v>132011688</v>
       </c>
       <c r="B36" t="n">
-        <v>91811</v>
+        <v>91848</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4217,13 +4217,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695475</v>
+        <v>695558</v>
       </c>
       <c r="R36" t="n">
-        <v>7036617</v>
+        <v>7036477</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132034138</v>
+        <v>132012332</v>
       </c>
       <c r="B39" t="n">
-        <v>79276</v>
+        <v>91848</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,40 +4492,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695488</v>
+        <v>695536</v>
       </c>
       <c r="R39" t="n">
-        <v>7036361</v>
+        <v>7036574</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4557,37 +4554,31 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132034143</v>
+        <v>132034138</v>
       </c>
       <c r="B40" t="n">
         <v>79276</v>
@@ -4616,16 +4607,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695430</v>
+        <v>695488</v>
       </c>
       <c r="R40" t="n">
-        <v>7036304</v>
+        <v>7036361</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4660,12 +4654,18 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132012332</v>
+        <v>132034143</v>
       </c>
       <c r="B42" t="n">
-        <v>91848</v>
+        <v>79276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,37 +4792,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695536</v>
+        <v>695430</v>
       </c>
       <c r="R42" t="n">
-        <v>7036574</v>
+        <v>7036304</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132012306</v>
       </c>
       <c r="B2" t="n">
-        <v>91811</v>
+        <v>91847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132007310</v>
       </c>
       <c r="B3" t="n">
-        <v>57093</v>
+        <v>57127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132034144</v>
       </c>
       <c r="B4" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>132014040</v>
       </c>
       <c r="B5" t="n">
-        <v>80254</v>
+        <v>80288</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,48 +1076,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132034114</v>
+        <v>132014573</v>
       </c>
       <c r="B6" t="n">
-        <v>91848</v>
+        <v>91868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695307</v>
+        <v>695342</v>
       </c>
       <c r="R6" t="n">
-        <v>7036500</v>
+        <v>7036654</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,22 +1161,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132034131</v>
+        <v>132034114</v>
       </c>
       <c r="B7" t="n">
-        <v>80381</v>
+        <v>91884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,37 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695355</v>
+        <v>695307</v>
       </c>
       <c r="R7" t="n">
-        <v>7036639</v>
+        <v>7036500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,24 +1252,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1289,48 +1270,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132014573</v>
+        <v>132034131</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>80415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695342</v>
+        <v>695355</v>
       </c>
       <c r="R8" t="n">
-        <v>7036654</v>
+        <v>7036639</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,18 +1352,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
         <v>132034129</v>
       </c>
       <c r="B9" t="n">
-        <v>80285</v>
+        <v>80319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>132034128</v>
       </c>
       <c r="B10" t="n">
-        <v>56483</v>
+        <v>56517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>132034124</v>
       </c>
       <c r="B11" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,45 +1709,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132034110</v>
+        <v>132034122</v>
       </c>
       <c r="B12" t="n">
-        <v>91811</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695453</v>
+        <v>695347</v>
       </c>
       <c r="R12" t="n">
-        <v>7036611</v>
+        <v>7036357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034122</v>
+        <v>132034126</v>
       </c>
       <c r="B13" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1847,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1849,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695347</v>
+        <v>695417</v>
       </c>
       <c r="R13" t="n">
-        <v>7036357</v>
+        <v>7036333</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,53 +1919,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034126</v>
+        <v>132034110</v>
       </c>
       <c r="B14" t="n">
-        <v>57911</v>
+        <v>91847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695417</v>
+        <v>695453</v>
       </c>
       <c r="R14" t="n">
-        <v>7036333</v>
+        <v>7036611</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
         <v>132034130</v>
       </c>
       <c r="B15" t="n">
-        <v>80381</v>
+        <v>80415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>132034120</v>
       </c>
       <c r="B16" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>132034132</v>
       </c>
       <c r="B17" t="n">
-        <v>80381</v>
+        <v>80415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034125</v>
+        <v>132034139</v>
       </c>
       <c r="B18" t="n">
-        <v>57911</v>
+        <v>79310</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,29 +2369,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2401,10 +2400,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695395</v>
+        <v>695472</v>
       </c>
       <c r="R18" t="n">
-        <v>7036336</v>
+        <v>7036445</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,6 +2444,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034139</v>
+        <v>132034142</v>
       </c>
       <c r="B19" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2492,23 +2492,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695472</v>
+        <v>695378</v>
       </c>
       <c r="R19" t="n">
-        <v>7036445</v>
+        <v>7036337</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,7 +2542,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2568,32 +2560,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034142</v>
+        <v>132034113</v>
       </c>
       <c r="B20" t="n">
-        <v>79276</v>
+        <v>91847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2603,10 +2595,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695378</v>
+        <v>695344</v>
       </c>
       <c r="R20" t="n">
-        <v>7036337</v>
+        <v>7036394</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,45 +2657,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034113</v>
+        <v>132034125</v>
       </c>
       <c r="B21" t="n">
-        <v>91811</v>
+        <v>57945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695344</v>
+        <v>695395</v>
       </c>
       <c r="R21" t="n">
-        <v>7036394</v>
+        <v>7036336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
         <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>91811</v>
+        <v>91847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>132034137</v>
       </c>
       <c r="B23" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>132034115</v>
       </c>
       <c r="B24" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>132034117</v>
       </c>
       <c r="B25" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132034140</v>
+        <v>132034127</v>
       </c>
       <c r="B26" t="n">
-        <v>79276</v>
+        <v>56517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,21 +3179,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695449</v>
+        <v>695353</v>
       </c>
       <c r="R26" t="n">
-        <v>7036505</v>
+        <v>7036635</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034141</v>
+        <v>132034140</v>
       </c>
       <c r="B27" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695346</v>
+        <v>695449</v>
       </c>
       <c r="R27" t="n">
-        <v>7036396</v>
+        <v>7036505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034121</v>
+        <v>132034141</v>
       </c>
       <c r="B28" t="n">
-        <v>57911</v>
+        <v>79310</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,42 +3373,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695332</v>
+        <v>695346</v>
       </c>
       <c r="R28" t="n">
-        <v>7036447</v>
+        <v>7036396</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034118</v>
+        <v>132034121</v>
       </c>
       <c r="B29" t="n">
-        <v>58073</v>
+        <v>57945</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3500,7 +3492,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3510,10 +3502,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695490</v>
+        <v>695332</v>
       </c>
       <c r="R29" t="n">
-        <v>7036280</v>
+        <v>7036447</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,19 +3535,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,10 +3564,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132034127</v>
+        <v>132034118</v>
       </c>
       <c r="B30" t="n">
-        <v>56483</v>
+        <v>58107</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,34 +3575,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695353</v>
+        <v>695490</v>
       </c>
       <c r="R30" t="n">
-        <v>7036635</v>
+        <v>7036280</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,9 +3640,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3682,7 +3682,7 @@
         <v>132034109</v>
       </c>
       <c r="B31" t="n">
-        <v>91811</v>
+        <v>91847</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>132013817</v>
       </c>
       <c r="B32" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>132034116</v>
       </c>
       <c r="B33" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>132013416</v>
       </c>
       <c r="B34" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>132012907</v>
       </c>
       <c r="B35" t="n">
-        <v>91811</v>
+        <v>91847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4182,48 +4182,51 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132011688</v>
+        <v>132014471</v>
       </c>
       <c r="B36" t="n">
-        <v>91848</v>
+        <v>80288</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695558</v>
+        <v>695346</v>
       </c>
       <c r="R36" t="n">
-        <v>7036477</v>
+        <v>7036647</v>
       </c>
       <c r="S36" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4261,6 +4264,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4279,10 +4283,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132014471</v>
+        <v>132014637</v>
       </c>
       <c r="B37" t="n">
-        <v>80254</v>
+        <v>80288</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4317,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695346</v>
+        <v>695362</v>
       </c>
       <c r="R37" t="n">
-        <v>7036647</v>
+        <v>7036633</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4380,51 +4384,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132014637</v>
+        <v>132011688</v>
       </c>
       <c r="B38" t="n">
-        <v>80254</v>
+        <v>91884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695362</v>
+        <v>695558</v>
       </c>
       <c r="R38" t="n">
-        <v>7036633</v>
+        <v>7036477</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4462,7 +4463,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>132012332</v>
       </c>
       <c r="B39" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>132034138</v>
       </c>
       <c r="B40" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>132034111</v>
       </c>
       <c r="B41" t="n">
-        <v>91811</v>
+        <v>91847</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>132034143</v>
       </c>
       <c r="B42" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>132006284</v>
       </c>
       <c r="B43" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>132034119</v>
       </c>
       <c r="B44" t="n">
-        <v>58073</v>
+        <v>58107</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>132034112</v>
       </c>
       <c r="B45" t="n">
-        <v>91811</v>
+        <v>91847</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>132034133</v>
       </c>
       <c r="B46" t="n">
-        <v>80381</v>
+        <v>80415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132012306</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132014040</v>
+        <v>132034144</v>
       </c>
       <c r="B4" t="n">
-        <v>80293</v>
+        <v>79317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,17 +908,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>695319</v>
+        <v>695495</v>
       </c>
       <c r="R4" t="n">
-        <v>7036604</v>
+        <v>7036285</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,44 +963,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132034144</v>
+        <v>132014040</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>80295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,17 +1009,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695495</v>
+        <v>695319</v>
       </c>
       <c r="R5" t="n">
-        <v>7036285</v>
+        <v>7036604</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,12 +1064,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
         <v>132034114</v>
       </c>
       <c r="B6" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,51 +1173,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132034131</v>
+        <v>132014573</v>
       </c>
       <c r="B7" t="n">
-        <v>80420</v>
+        <v>91876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695355</v>
+        <v>695342</v>
       </c>
       <c r="R7" t="n">
-        <v>7036639</v>
+        <v>7036654</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,82 +1252,69 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132014573</v>
+        <v>132034131</v>
       </c>
       <c r="B8" t="n">
-        <v>91873</v>
+        <v>80422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695342</v>
+        <v>695355</v>
       </c>
       <c r="R8" t="n">
-        <v>7036654</v>
+        <v>7036639</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,18 +1352,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
         <v>132034129</v>
       </c>
       <c r="B9" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1709,53 +1709,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132034122</v>
+        <v>132034110</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>91855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695347</v>
+        <v>695453</v>
       </c>
       <c r="R12" t="n">
-        <v>7036357</v>
+        <v>7036611</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,45 +1911,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034110</v>
+        <v>132034122</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695453</v>
+        <v>695347</v>
       </c>
       <c r="R14" t="n">
-        <v>7036611</v>
+        <v>7036357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132034130</v>
+        <v>132034120</v>
       </c>
       <c r="B15" t="n">
-        <v>80420</v>
+        <v>57945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,26 +2027,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2054,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695359</v>
+        <v>695450</v>
       </c>
       <c r="R15" t="n">
-        <v>7036639</v>
+        <v>7036585</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,24 +2103,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2132,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132034120</v>
+        <v>132034130</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>80422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,31 +2132,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2175,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695450</v>
+        <v>695359</v>
       </c>
       <c r="R16" t="n">
-        <v>7036585</v>
+        <v>7036639</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,8 +2203,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2240,7 +2240,7 @@
         <v>132034132</v>
       </c>
       <c r="B17" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>132034139</v>
       </c>
       <c r="B18" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>132034142</v>
       </c>
       <c r="B19" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>132034113</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132034137</v>
+        <v>132034115</v>
       </c>
       <c r="B23" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2870,34 +2870,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695380</v>
+        <v>695321</v>
       </c>
       <c r="R23" t="n">
-        <v>7036661</v>
+        <v>7036547</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,6 +2934,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,10 +2965,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132034115</v>
+        <v>132034137</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2967,38 +2976,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695321</v>
+        <v>695380</v>
       </c>
       <c r="R24" t="n">
-        <v>7036547</v>
+        <v>7036661</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,11 +3036,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132034121</v>
+        <v>132034141</v>
       </c>
       <c r="B26" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,42 +3179,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695332</v>
+        <v>695346</v>
       </c>
       <c r="R26" t="n">
-        <v>7036447</v>
+        <v>7036396</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3273,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034140</v>
+        <v>132034118</v>
       </c>
       <c r="B27" t="n">
-        <v>79315</v>
+        <v>58109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,34 +3276,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695449</v>
+        <v>695490</v>
       </c>
       <c r="R27" t="n">
-        <v>7036505</v>
+        <v>7036280</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,9 +3341,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3370,10 +3380,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034141</v>
+        <v>132034140</v>
       </c>
       <c r="B28" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3405,10 +3415,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695346</v>
+        <v>695449</v>
       </c>
       <c r="R28" t="n">
-        <v>7036396</v>
+        <v>7036505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,10 +3477,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034118</v>
+        <v>132034127</v>
       </c>
       <c r="B29" t="n">
-        <v>58107</v>
+        <v>56517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,42 +3488,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695490</v>
+        <v>695353</v>
       </c>
       <c r="R29" t="n">
-        <v>7036280</v>
+        <v>7036635</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,19 +3545,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,10 +3574,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132034127</v>
+        <v>132034121</v>
       </c>
       <c r="B30" t="n">
-        <v>56517</v>
+        <v>57945</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,34 +3585,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695353</v>
+        <v>695332</v>
       </c>
       <c r="R30" t="n">
-        <v>7036635</v>
+        <v>7036447</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3682,7 +3682,7 @@
         <v>132034109</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>132013817</v>
       </c>
       <c r="B32" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,48 +4085,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132014471</v>
+        <v>132012907</v>
       </c>
       <c r="B35" t="n">
-        <v>80293</v>
+        <v>91855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695346</v>
+        <v>695475</v>
       </c>
       <c r="R35" t="n">
-        <v>7036647</v>
+        <v>7036617</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4167,7 +4164,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4186,10 +4182,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132014637</v>
+        <v>132014471</v>
       </c>
       <c r="B36" t="n">
-        <v>80293</v>
+        <v>80295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4224,10 +4220,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695362</v>
+        <v>695346</v>
       </c>
       <c r="R36" t="n">
-        <v>7036633</v>
+        <v>7036647</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4287,48 +4283,51 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132011688</v>
+        <v>132014637</v>
       </c>
       <c r="B37" t="n">
-        <v>91889</v>
+        <v>80295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695558</v>
+        <v>695362</v>
       </c>
       <c r="R37" t="n">
-        <v>7036477</v>
+        <v>7036633</v>
       </c>
       <c r="S37" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4366,6 +4365,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4384,32 +4384,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132012907</v>
+        <v>132011688</v>
       </c>
       <c r="B38" t="n">
-        <v>91852</v>
+        <v>91892</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695475</v>
+        <v>695558</v>
       </c>
       <c r="R38" t="n">
-        <v>7036617</v>
+        <v>7036477</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>132034138</v>
       </c>
       <c r="B39" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132034111</v>
+        <v>132034143</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>79317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695315</v>
+        <v>695430</v>
       </c>
       <c r="R40" t="n">
-        <v>7036513</v>
+        <v>7036304</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132034143</v>
+        <v>132012332</v>
       </c>
       <c r="B41" t="n">
-        <v>79315</v>
+        <v>91892</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4695,37 +4695,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695430</v>
+        <v>695536</v>
       </c>
       <c r="R41" t="n">
-        <v>7036304</v>
+        <v>7036574</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4769,22 +4769,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132006284</v>
+        <v>132034111</v>
       </c>
       <c r="B42" t="n">
-        <v>57136</v>
+        <v>91855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,42 +4792,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695748</v>
+        <v>695315</v>
       </c>
       <c r="R42" t="n">
-        <v>7036138</v>
+        <v>7036513</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4871,57 +4866,62 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132012332</v>
+        <v>132006284</v>
       </c>
       <c r="B43" t="n">
-        <v>91889</v>
+        <v>57136</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695536</v>
+        <v>695748</v>
       </c>
       <c r="R43" t="n">
-        <v>7036574</v>
+        <v>7036138</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>132034119</v>
       </c>
       <c r="B44" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>132034112</v>
       </c>
       <c r="B45" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>132034133</v>
       </c>
       <c r="B46" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -1076,48 +1076,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132034114</v>
+        <v>132014573</v>
       </c>
       <c r="B6" t="n">
-        <v>91892</v>
+        <v>91876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695307</v>
+        <v>695342</v>
       </c>
       <c r="R6" t="n">
-        <v>7036500</v>
+        <v>7036654</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,60 +1161,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132014573</v>
+        <v>132034114</v>
       </c>
       <c r="B7" t="n">
-        <v>91876</v>
+        <v>91892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695342</v>
+        <v>695307</v>
       </c>
       <c r="R7" t="n">
-        <v>7036654</v>
+        <v>7036500</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,12 +1258,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132034120</v>
+        <v>132034130</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>80422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,31 +2027,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2059,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695450</v>
+        <v>695359</v>
       </c>
       <c r="R15" t="n">
-        <v>7036585</v>
+        <v>7036639</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,8 +2098,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2121,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132034130</v>
+        <v>132034120</v>
       </c>
       <c r="B16" t="n">
-        <v>80422</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,26 +2143,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2159,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695359</v>
+        <v>695450</v>
       </c>
       <c r="R16" t="n">
-        <v>7036639</v>
+        <v>7036585</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,24 +2219,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2762,48 +2762,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132012638</v>
+        <v>132034117</v>
       </c>
       <c r="B22" t="n">
-        <v>91855</v>
+        <v>57948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695461</v>
+        <v>695633</v>
       </c>
       <c r="R22" t="n">
-        <v>7036590</v>
+        <v>7036036</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2833,6 +2837,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,12 +2856,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2965,48 +2974,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132034137</v>
+        <v>132012638</v>
       </c>
       <c r="B24" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695380</v>
+        <v>695461</v>
       </c>
       <c r="R24" t="n">
-        <v>7036661</v>
+        <v>7036590</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3050,22 +3059,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132034117</v>
+        <v>132034137</v>
       </c>
       <c r="B25" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3073,38 +3082,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695633</v>
+        <v>695380</v>
       </c>
       <c r="R25" t="n">
-        <v>7036036</v>
+        <v>7036661</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3137,11 +3142,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3265,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034118</v>
+        <v>132034140</v>
       </c>
       <c r="B27" t="n">
-        <v>58109</v>
+        <v>79317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3276,42 +3276,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695490</v>
+        <v>695449</v>
       </c>
       <c r="R27" t="n">
-        <v>7036280</v>
+        <v>7036505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,19 +3333,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3380,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034140</v>
+        <v>132034121</v>
       </c>
       <c r="B28" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3391,34 +3373,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695449</v>
+        <v>695332</v>
       </c>
       <c r="R28" t="n">
-        <v>7036505</v>
+        <v>7036447</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034127</v>
+        <v>132034118</v>
       </c>
       <c r="B29" t="n">
-        <v>56517</v>
+        <v>58109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3488,34 +3478,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695353</v>
+        <v>695490</v>
       </c>
       <c r="R29" t="n">
-        <v>7036635</v>
+        <v>7036280</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,9 +3543,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3574,10 +3582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132034121</v>
+        <v>132034127</v>
       </c>
       <c r="B30" t="n">
-        <v>57945</v>
+        <v>56517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3585,42 +3593,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695332</v>
+        <v>695353</v>
       </c>
       <c r="R30" t="n">
-        <v>7036447</v>
+        <v>7036635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132034130</v>
+        <v>132034120</v>
       </c>
       <c r="B15" t="n">
-        <v>80422</v>
+        <v>57945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,26 +2027,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2054,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695359</v>
+        <v>695450</v>
       </c>
       <c r="R15" t="n">
-        <v>7036639</v>
+        <v>7036585</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,24 +2103,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2132,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132034120</v>
+        <v>132034130</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>80422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,31 +2132,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2175,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695450</v>
+        <v>695359</v>
       </c>
       <c r="R16" t="n">
-        <v>7036585</v>
+        <v>7036639</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,8 +2203,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2762,52 +2762,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132034117</v>
+        <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695633</v>
+        <v>695461</v>
       </c>
       <c r="R22" t="n">
-        <v>7036036</v>
+        <v>7036590</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2837,11 +2833,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2856,12 +2847,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2974,48 +2965,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132012638</v>
+        <v>132034137</v>
       </c>
       <c r="B24" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695461</v>
+        <v>695380</v>
       </c>
       <c r="R24" t="n">
-        <v>7036590</v>
+        <v>7036661</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3059,22 +3050,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132034137</v>
+        <v>132034117</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,34 +3073,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695380</v>
+        <v>695633</v>
       </c>
       <c r="R25" t="n">
-        <v>7036661</v>
+        <v>7036036</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3142,6 +3137,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3265,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034140</v>
+        <v>132034118</v>
       </c>
       <c r="B27" t="n">
-        <v>79317</v>
+        <v>58109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3276,34 +3276,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695449</v>
+        <v>695490</v>
       </c>
       <c r="R27" t="n">
-        <v>7036505</v>
+        <v>7036280</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3333,9 +3341,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,10 +3380,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034121</v>
+        <v>132034140</v>
       </c>
       <c r="B28" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,42 +3391,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695332</v>
+        <v>695449</v>
       </c>
       <c r="R28" t="n">
-        <v>7036447</v>
+        <v>7036505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,10 +3477,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034118</v>
+        <v>132034127</v>
       </c>
       <c r="B29" t="n">
-        <v>58109</v>
+        <v>56517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,42 +3488,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695490</v>
+        <v>695353</v>
       </c>
       <c r="R29" t="n">
-        <v>7036280</v>
+        <v>7036635</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,19 +3545,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,10 +3574,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132034127</v>
+        <v>132034121</v>
       </c>
       <c r="B30" t="n">
-        <v>56517</v>
+        <v>57945</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,34 +3585,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695353</v>
+        <v>695332</v>
       </c>
       <c r="R30" t="n">
-        <v>7036635</v>
+        <v>7036447</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -1076,48 +1076,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132014573</v>
+        <v>132034131</v>
       </c>
       <c r="B6" t="n">
-        <v>91876</v>
+        <v>80422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695342</v>
+        <v>695355</v>
       </c>
       <c r="R6" t="n">
-        <v>7036654</v>
+        <v>7036639</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1155,66 +1158,82 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132034114</v>
+        <v>132014573</v>
       </c>
       <c r="B7" t="n">
-        <v>91892</v>
+        <v>91876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695307</v>
+        <v>695342</v>
       </c>
       <c r="R7" t="n">
-        <v>7036500</v>
+        <v>7036654</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,22 +1277,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034131</v>
+        <v>132034114</v>
       </c>
       <c r="B8" t="n">
-        <v>80422</v>
+        <v>91892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,37 +1300,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695355</v>
+        <v>695307</v>
       </c>
       <c r="R8" t="n">
-        <v>7036639</v>
+        <v>7036500</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,24 +1368,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1806,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034126</v>
+        <v>132034122</v>
       </c>
       <c r="B13" t="n">
         <v>57945</v>
@@ -1839,7 +1839,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695417</v>
+        <v>695347</v>
       </c>
       <c r="R13" t="n">
-        <v>7036333</v>
+        <v>7036357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034122</v>
+        <v>132034126</v>
       </c>
       <c r="B14" t="n">
         <v>57945</v>
@@ -1944,7 +1944,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695347</v>
+        <v>695417</v>
       </c>
       <c r="R14" t="n">
-        <v>7036357</v>
+        <v>7036333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132034120</v>
+        <v>132034130</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>80422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,31 +2027,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2059,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695450</v>
+        <v>695359</v>
       </c>
       <c r="R15" t="n">
-        <v>7036585</v>
+        <v>7036639</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,8 +2098,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2121,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132034130</v>
+        <v>132034120</v>
       </c>
       <c r="B16" t="n">
-        <v>80422</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,26 +2143,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2159,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695359</v>
+        <v>695450</v>
       </c>
       <c r="R16" t="n">
-        <v>7036639</v>
+        <v>7036585</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,24 +2219,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2358,52 +2358,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034139</v>
+        <v>132034113</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695472</v>
+        <v>695344</v>
       </c>
       <c r="R18" t="n">
-        <v>7036445</v>
+        <v>7036394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,7 +2437,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2463,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034142</v>
+        <v>132034125</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,34 +2466,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695378</v>
+        <v>695395</v>
       </c>
       <c r="R19" t="n">
-        <v>7036337</v>
+        <v>7036336</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,45 +2560,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034113</v>
+        <v>132034139</v>
       </c>
       <c r="B20" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695344</v>
+        <v>695472</v>
       </c>
       <c r="R20" t="n">
-        <v>7036394</v>
+        <v>7036445</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,6 +2646,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2657,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034125</v>
+        <v>132034142</v>
       </c>
       <c r="B21" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,42 +2676,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695395</v>
+        <v>695378</v>
       </c>
       <c r="R21" t="n">
-        <v>7036336</v>
+        <v>7036337</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,48 +2762,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132012638</v>
+        <v>132034115</v>
       </c>
       <c r="B22" t="n">
-        <v>91855</v>
+        <v>57948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695461</v>
+        <v>695321</v>
       </c>
       <c r="R22" t="n">
-        <v>7036590</v>
+        <v>7036547</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2833,6 +2837,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,19 +2856,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132034115</v>
+        <v>132034117</v>
       </c>
       <c r="B23" t="n">
         <v>57948</v>
@@ -2898,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695321</v>
+        <v>695633</v>
       </c>
       <c r="R23" t="n">
-        <v>7036547</v>
+        <v>7036036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,7 +2947,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2965,48 +2974,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132034137</v>
+        <v>132012638</v>
       </c>
       <c r="B24" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695380</v>
+        <v>695461</v>
       </c>
       <c r="R24" t="n">
-        <v>7036661</v>
+        <v>7036590</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3050,22 +3059,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132034117</v>
+        <v>132034137</v>
       </c>
       <c r="B25" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3073,38 +3082,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695633</v>
+        <v>695380</v>
       </c>
       <c r="R25" t="n">
-        <v>7036036</v>
+        <v>7036661</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3137,11 +3142,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,7 +3168,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132034141</v>
+        <v>132034140</v>
       </c>
       <c r="B26" t="n">
         <v>79317</v>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695346</v>
+        <v>695449</v>
       </c>
       <c r="R26" t="n">
-        <v>7036396</v>
+        <v>7036505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034118</v>
+        <v>132034141</v>
       </c>
       <c r="B27" t="n">
-        <v>58109</v>
+        <v>79317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3276,42 +3276,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695490</v>
+        <v>695346</v>
       </c>
       <c r="R27" t="n">
-        <v>7036280</v>
+        <v>7036396</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,19 +3333,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3380,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034140</v>
+        <v>132034127</v>
       </c>
       <c r="B28" t="n">
-        <v>79317</v>
+        <v>56517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3391,21 +3373,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3415,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695449</v>
+        <v>695353</v>
       </c>
       <c r="R28" t="n">
-        <v>7036505</v>
+        <v>7036635</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034127</v>
+        <v>132034118</v>
       </c>
       <c r="B29" t="n">
-        <v>56517</v>
+        <v>58109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3488,34 +3470,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695353</v>
+        <v>695490</v>
       </c>
       <c r="R29" t="n">
-        <v>7036635</v>
+        <v>7036280</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,9 +3535,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3679,48 +3679,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132034109</v>
+        <v>132013817</v>
       </c>
       <c r="B31" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695562</v>
+        <v>695302</v>
       </c>
       <c r="R31" t="n">
-        <v>7036322</v>
+        <v>7036682</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3764,60 +3764,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132013817</v>
+        <v>132034109</v>
       </c>
       <c r="B32" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695302</v>
+        <v>695562</v>
       </c>
       <c r="R32" t="n">
-        <v>7036682</v>
+        <v>7036322</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4085,45 +4085,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132012907</v>
+        <v>132014471</v>
       </c>
       <c r="B35" t="n">
-        <v>91855</v>
+        <v>80295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695475</v>
+        <v>695346</v>
       </c>
       <c r="R35" t="n">
-        <v>7036617</v>
+        <v>7036647</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4164,6 +4167,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4182,7 +4186,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132014471</v>
+        <v>132014637</v>
       </c>
       <c r="B36" t="n">
         <v>80295</v>
@@ -4220,10 +4224,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695346</v>
+        <v>695362</v>
       </c>
       <c r="R36" t="n">
-        <v>7036647</v>
+        <v>7036633</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4283,51 +4287,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132014637</v>
+        <v>132011688</v>
       </c>
       <c r="B37" t="n">
-        <v>80295</v>
+        <v>91892</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695362</v>
+        <v>695558</v>
       </c>
       <c r="R37" t="n">
-        <v>7036633</v>
+        <v>7036477</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4365,7 +4366,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4384,32 +4384,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132011688</v>
+        <v>132012907</v>
       </c>
       <c r="B38" t="n">
-        <v>91892</v>
+        <v>91855</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695558</v>
+        <v>695475</v>
       </c>
       <c r="R38" t="n">
-        <v>7036477</v>
+        <v>7036617</v>
       </c>
       <c r="S38" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132034138</v>
+        <v>132034143</v>
       </c>
       <c r="B39" t="n">
         <v>79317</v>
@@ -4510,19 +4510,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695488</v>
+        <v>695430</v>
       </c>
       <c r="R39" t="n">
-        <v>7036361</v>
+        <v>7036304</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,18 +4554,12 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4587,32 +4578,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132034143</v>
+        <v>132034111</v>
       </c>
       <c r="B40" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4622,10 +4613,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695430</v>
+        <v>695315</v>
       </c>
       <c r="R40" t="n">
-        <v>7036304</v>
+        <v>7036513</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4684,10 +4675,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132012332</v>
+        <v>132034138</v>
       </c>
       <c r="B41" t="n">
-        <v>91892</v>
+        <v>79317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4695,37 +4686,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695536</v>
+        <v>695488</v>
       </c>
       <c r="R41" t="n">
-        <v>7036574</v>
+        <v>7036361</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4757,72 +4751,78 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132034111</v>
+        <v>132012332</v>
       </c>
       <c r="B42" t="n">
-        <v>91855</v>
+        <v>91892</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695315</v>
+        <v>695536</v>
       </c>
       <c r="R42" t="n">
-        <v>7036513</v>
+        <v>7036574</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -2358,45 +2358,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034113</v>
+        <v>132034139</v>
       </c>
       <c r="B18" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695344</v>
+        <v>695472</v>
       </c>
       <c r="R18" t="n">
-        <v>7036394</v>
+        <v>7036445</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,6 +2444,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2455,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034125</v>
+        <v>132034142</v>
       </c>
       <c r="B19" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,42 +2474,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695395</v>
+        <v>695378</v>
       </c>
       <c r="R19" t="n">
-        <v>7036336</v>
+        <v>7036337</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,52 +2560,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034139</v>
+        <v>132034113</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695472</v>
+        <v>695344</v>
       </c>
       <c r="R20" t="n">
-        <v>7036445</v>
+        <v>7036394</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,7 +2639,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2665,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034142</v>
+        <v>132034125</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,34 +2668,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695378</v>
+        <v>695395</v>
       </c>
       <c r="R21" t="n">
-        <v>7036337</v>
+        <v>7036336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132034143</v>
+        <v>132034138</v>
       </c>
       <c r="B39" t="n">
         <v>79317</v>
@@ -4510,16 +4510,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695430</v>
+        <v>695488</v>
       </c>
       <c r="R39" t="n">
-        <v>7036304</v>
+        <v>7036361</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,12 +4557,18 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4675,51 +4684,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132034138</v>
+        <v>132006284</v>
       </c>
       <c r="B41" t="n">
-        <v>79317</v>
+        <v>57136</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695488</v>
+        <v>695748</v>
       </c>
       <c r="R41" t="n">
-        <v>7036361</v>
+        <v>7036138</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4751,40 +4762,34 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132012332</v>
+        <v>132034143</v>
       </c>
       <c r="B42" t="n">
-        <v>91892</v>
+        <v>79317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,37 +4797,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695536</v>
+        <v>695430</v>
       </c>
       <c r="R42" t="n">
-        <v>7036574</v>
+        <v>7036304</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4866,62 +4871,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132006284</v>
+        <v>132012332</v>
       </c>
       <c r="B43" t="n">
-        <v>57136</v>
+        <v>91892</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695748</v>
+        <v>695536</v>
       </c>
       <c r="R43" t="n">
-        <v>7036138</v>
+        <v>7036574</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -1709,45 +1709,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132034110</v>
+        <v>132034122</v>
       </c>
       <c r="B12" t="n">
-        <v>91855</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695453</v>
+        <v>695347</v>
       </c>
       <c r="R12" t="n">
-        <v>7036611</v>
+        <v>7036357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,7 +1814,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034122</v>
+        <v>132034126</v>
       </c>
       <c r="B13" t="n">
         <v>57945</v>
@@ -1839,7 +1847,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1849,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695347</v>
+        <v>695417</v>
       </c>
       <c r="R13" t="n">
-        <v>7036357</v>
+        <v>7036333</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,53 +1919,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034126</v>
+        <v>132034110</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>91855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695417</v>
+        <v>695453</v>
       </c>
       <c r="R14" t="n">
-        <v>7036333</v>
+        <v>7036611</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2358,52 +2358,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034139</v>
+        <v>132034113</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695472</v>
+        <v>695344</v>
       </c>
       <c r="R18" t="n">
-        <v>7036445</v>
+        <v>7036394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,7 +2437,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2463,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034142</v>
+        <v>132034125</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,34 +2466,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695378</v>
+        <v>695395</v>
       </c>
       <c r="R19" t="n">
-        <v>7036337</v>
+        <v>7036336</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,45 +2560,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034113</v>
+        <v>132034139</v>
       </c>
       <c r="B20" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695344</v>
+        <v>695472</v>
       </c>
       <c r="R20" t="n">
-        <v>7036394</v>
+        <v>7036445</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,6 +2646,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2657,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034125</v>
+        <v>132034142</v>
       </c>
       <c r="B21" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,42 +2676,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695395</v>
+        <v>695378</v>
       </c>
       <c r="R21" t="n">
-        <v>7036336</v>
+        <v>7036337</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132034138</v>
+        <v>132034143</v>
       </c>
       <c r="B39" t="n">
         <v>79317</v>
@@ -4510,19 +4510,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695488</v>
+        <v>695430</v>
       </c>
       <c r="R39" t="n">
-        <v>7036361</v>
+        <v>7036304</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,18 +4554,12 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4684,53 +4675,51 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132006284</v>
+        <v>132034138</v>
       </c>
       <c r="B41" t="n">
-        <v>57136</v>
+        <v>79317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695748</v>
+        <v>695488</v>
       </c>
       <c r="R41" t="n">
-        <v>7036138</v>
+        <v>7036361</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4762,34 +4751,40 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132034143</v>
+        <v>132012332</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4797,37 +4792,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695430</v>
+        <v>695536</v>
       </c>
       <c r="R42" t="n">
-        <v>7036304</v>
+        <v>7036574</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4871,57 +4866,62 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132012332</v>
+        <v>132006284</v>
       </c>
       <c r="B43" t="n">
-        <v>91892</v>
+        <v>57136</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695536</v>
+        <v>695748</v>
       </c>
       <c r="R43" t="n">
-        <v>7036574</v>
+        <v>7036138</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -1709,53 +1709,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132034122</v>
+        <v>132034110</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>91855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695347</v>
+        <v>695453</v>
       </c>
       <c r="R12" t="n">
-        <v>7036357</v>
+        <v>7036611</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034126</v>
+        <v>132034122</v>
       </c>
       <c r="B13" t="n">
         <v>57945</v>
@@ -1847,7 +1839,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1857,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695417</v>
+        <v>695347</v>
       </c>
       <c r="R13" t="n">
-        <v>7036333</v>
+        <v>7036357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,45 +1911,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034110</v>
+        <v>132034126</v>
       </c>
       <c r="B14" t="n">
-        <v>91855</v>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695453</v>
+        <v>695417</v>
       </c>
       <c r="R14" t="n">
-        <v>7036611</v>
+        <v>7036333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034127</v>
+        <v>132034118</v>
       </c>
       <c r="B28" t="n">
-        <v>56517</v>
+        <v>58109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,34 +3373,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695353</v>
+        <v>695490</v>
       </c>
       <c r="R28" t="n">
-        <v>7036635</v>
+        <v>7036280</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,9 +3438,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3459,10 +3477,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034118</v>
+        <v>132034121</v>
       </c>
       <c r="B29" t="n">
-        <v>58109</v>
+        <v>57945</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3470,21 +3488,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3492,7 +3510,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3502,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695490</v>
+        <v>695332</v>
       </c>
       <c r="R29" t="n">
-        <v>7036280</v>
+        <v>7036447</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,19 +3553,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3574,10 +3582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132034121</v>
+        <v>132034127</v>
       </c>
       <c r="B30" t="n">
-        <v>57945</v>
+        <v>56517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3585,42 +3593,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695332</v>
+        <v>695353</v>
       </c>
       <c r="R30" t="n">
-        <v>7036447</v>
+        <v>7036635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4085,48 +4085,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132014471</v>
+        <v>132012907</v>
       </c>
       <c r="B35" t="n">
-        <v>80295</v>
+        <v>91855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695346</v>
+        <v>695475</v>
       </c>
       <c r="R35" t="n">
-        <v>7036647</v>
+        <v>7036617</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4167,7 +4164,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4186,7 +4182,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132014637</v>
+        <v>132014471</v>
       </c>
       <c r="B36" t="n">
         <v>80295</v>
@@ -4224,10 +4220,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695362</v>
+        <v>695346</v>
       </c>
       <c r="R36" t="n">
-        <v>7036633</v>
+        <v>7036647</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4287,48 +4283,51 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132011688</v>
+        <v>132014637</v>
       </c>
       <c r="B37" t="n">
-        <v>91892</v>
+        <v>80295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695558</v>
+        <v>695362</v>
       </c>
       <c r="R37" t="n">
-        <v>7036477</v>
+        <v>7036633</v>
       </c>
       <c r="S37" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4366,6 +4365,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4384,32 +4384,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132012907</v>
+        <v>132011688</v>
       </c>
       <c r="B38" t="n">
-        <v>91855</v>
+        <v>91892</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695475</v>
+        <v>695558</v>
       </c>
       <c r="R38" t="n">
-        <v>7036617</v>
+        <v>7036477</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132012306</v>
       </c>
       <c r="B2" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132007310</v>
       </c>
       <c r="B3" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132034144</v>
       </c>
       <c r="B4" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>132014040</v>
       </c>
       <c r="B5" t="n">
-        <v>80295</v>
+        <v>80297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>132034131</v>
       </c>
       <c r="B6" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,48 +1192,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132014573</v>
+        <v>132034114</v>
       </c>
       <c r="B7" t="n">
-        <v>91876</v>
+        <v>91898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695342</v>
+        <v>695307</v>
       </c>
       <c r="R7" t="n">
-        <v>7036654</v>
+        <v>7036500</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1277,60 +1277,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034114</v>
+        <v>132014573</v>
       </c>
       <c r="B8" t="n">
-        <v>91892</v>
+        <v>91882</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695307</v>
+        <v>695342</v>
       </c>
       <c r="R8" t="n">
-        <v>7036500</v>
+        <v>7036654</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1374,12 +1374,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
         <v>132034129</v>
       </c>
       <c r="B9" t="n">
-        <v>80326</v>
+        <v>80328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>132034128</v>
       </c>
       <c r="B10" t="n">
-        <v>56517</v>
+        <v>56518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>132034124</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132034110</v>
       </c>
       <c r="B12" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034122</v>
+        <v>132034126</v>
       </c>
       <c r="B13" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695347</v>
+        <v>695417</v>
       </c>
       <c r="R13" t="n">
-        <v>7036357</v>
+        <v>7036333</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034126</v>
+        <v>132034122</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695417</v>
+        <v>695347</v>
       </c>
       <c r="R14" t="n">
-        <v>7036333</v>
+        <v>7036357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
         <v>132034130</v>
       </c>
       <c r="B15" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>132034120</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>132034132</v>
       </c>
       <c r="B17" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,45 +2358,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034113</v>
+        <v>132034125</v>
       </c>
       <c r="B18" t="n">
-        <v>91855</v>
+        <v>57946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695344</v>
+        <v>695395</v>
       </c>
       <c r="R18" t="n">
-        <v>7036394</v>
+        <v>7036336</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034125</v>
+        <v>132034139</v>
       </c>
       <c r="B19" t="n">
-        <v>57945</v>
+        <v>79319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,29 +2474,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2498,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695395</v>
+        <v>695472</v>
       </c>
       <c r="R19" t="n">
-        <v>7036336</v>
+        <v>7036445</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,6 +2549,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2560,10 +2568,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034139</v>
+        <v>132034142</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2589,23 +2597,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695472</v>
+        <v>695378</v>
       </c>
       <c r="R20" t="n">
-        <v>7036445</v>
+        <v>7036337</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,7 +2647,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2665,32 +2665,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034142</v>
+        <v>132034113</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>91861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695378</v>
+        <v>695344</v>
       </c>
       <c r="R21" t="n">
-        <v>7036337</v>
+        <v>7036394</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,52 +2762,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132034115</v>
+        <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>91861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695321</v>
+        <v>695461</v>
       </c>
       <c r="R22" t="n">
-        <v>7036547</v>
+        <v>7036590</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2837,11 +2833,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2856,22 +2847,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132034117</v>
+        <v>132034137</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,38 +2870,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>695633</v>
+        <v>695380</v>
       </c>
       <c r="R23" t="n">
-        <v>7036036</v>
+        <v>7036661</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,11 +2930,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,48 +2956,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132012638</v>
+        <v>132034115</v>
       </c>
       <c r="B24" t="n">
-        <v>91855</v>
+        <v>57949</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695461</v>
+        <v>695321</v>
       </c>
       <c r="R24" t="n">
-        <v>7036590</v>
+        <v>7036547</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3045,6 +3031,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3059,22 +3050,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132034137</v>
+        <v>132034117</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,34 +3073,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695380</v>
+        <v>695633</v>
       </c>
       <c r="R25" t="n">
-        <v>7036661</v>
+        <v>7036036</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3142,6 +3137,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3171,7 +3171,7 @@
         <v>132034140</v>
       </c>
       <c r="B26" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>132034141</v>
       </c>
       <c r="B27" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034118</v>
+        <v>132034121</v>
       </c>
       <c r="B28" t="n">
-        <v>58109</v>
+        <v>57946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695490</v>
+        <v>695332</v>
       </c>
       <c r="R28" t="n">
-        <v>7036280</v>
+        <v>7036447</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,19 +3438,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3477,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034121</v>
+        <v>132034118</v>
       </c>
       <c r="B29" t="n">
-        <v>57945</v>
+        <v>58110</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3488,21 +3478,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3510,7 +3500,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3520,10 +3510,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695332</v>
+        <v>695490</v>
       </c>
       <c r="R29" t="n">
-        <v>7036447</v>
+        <v>7036280</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,9 +3543,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3585,7 +3585,7 @@
         <v>132034127</v>
       </c>
       <c r="B30" t="n">
-        <v>56517</v>
+        <v>56518</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,48 +3679,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132013817</v>
+        <v>132034109</v>
       </c>
       <c r="B31" t="n">
-        <v>79317</v>
+        <v>91861</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695302</v>
+        <v>695562</v>
       </c>
       <c r="R31" t="n">
-        <v>7036682</v>
+        <v>7036322</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3764,60 +3764,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132034109</v>
+        <v>132013817</v>
       </c>
       <c r="B32" t="n">
-        <v>91855</v>
+        <v>79319</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695562</v>
+        <v>695302</v>
       </c>
       <c r="R32" t="n">
-        <v>7036322</v>
+        <v>7036682</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3876,7 +3876,7 @@
         <v>132034116</v>
       </c>
       <c r="B33" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>132013416</v>
       </c>
       <c r="B34" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,45 +4085,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132012907</v>
+        <v>132014471</v>
       </c>
       <c r="B35" t="n">
-        <v>91855</v>
+        <v>80297</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695475</v>
+        <v>695346</v>
       </c>
       <c r="R35" t="n">
-        <v>7036617</v>
+        <v>7036647</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4164,6 +4167,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4182,10 +4186,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132014471</v>
+        <v>132014637</v>
       </c>
       <c r="B36" t="n">
-        <v>80295</v>
+        <v>80297</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,10 +4224,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695346</v>
+        <v>695362</v>
       </c>
       <c r="R36" t="n">
-        <v>7036647</v>
+        <v>7036633</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4283,51 +4287,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132014637</v>
+        <v>132011688</v>
       </c>
       <c r="B37" t="n">
-        <v>80295</v>
+        <v>91898</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695362</v>
+        <v>695558</v>
       </c>
       <c r="R37" t="n">
-        <v>7036633</v>
+        <v>7036477</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4365,7 +4366,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4384,32 +4384,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132011688</v>
+        <v>132012907</v>
       </c>
       <c r="B38" t="n">
-        <v>91892</v>
+        <v>91861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695558</v>
+        <v>695475</v>
       </c>
       <c r="R38" t="n">
-        <v>7036477</v>
+        <v>7036617</v>
       </c>
       <c r="S38" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132034143</v>
+        <v>132034138</v>
       </c>
       <c r="B39" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,16 +4510,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695430</v>
+        <v>695488</v>
       </c>
       <c r="R39" t="n">
-        <v>7036304</v>
+        <v>7036361</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,12 +4557,18 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4581,7 +4590,7 @@
         <v>132034111</v>
       </c>
       <c r="B40" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,10 +4684,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132034138</v>
+        <v>132034143</v>
       </c>
       <c r="B41" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4704,19 +4713,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695488</v>
+        <v>695430</v>
       </c>
       <c r="R41" t="n">
-        <v>7036361</v>
+        <v>7036304</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4751,18 +4757,12 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4781,45 +4781,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132012332</v>
+        <v>132006284</v>
       </c>
       <c r="B42" t="n">
-        <v>91892</v>
+        <v>57137</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695536</v>
+        <v>695748</v>
       </c>
       <c r="R42" t="n">
-        <v>7036574</v>
+        <v>7036138</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4878,50 +4883,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132006284</v>
+        <v>132012332</v>
       </c>
       <c r="B43" t="n">
-        <v>57136</v>
+        <v>91898</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695748</v>
+        <v>695536</v>
       </c>
       <c r="R43" t="n">
-        <v>7036138</v>
+        <v>7036574</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>132034119</v>
       </c>
       <c r="B44" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>132034112</v>
       </c>
       <c r="B45" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>132034133</v>
       </c>
       <c r="B46" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132034130</v>
+        <v>132034120</v>
       </c>
       <c r="B15" t="n">
-        <v>80424</v>
+        <v>57946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,26 +2027,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2054,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695359</v>
+        <v>695450</v>
       </c>
       <c r="R15" t="n">
-        <v>7036639</v>
+        <v>7036585</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,24 +2103,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2132,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132034120</v>
+        <v>132034130</v>
       </c>
       <c r="B16" t="n">
-        <v>57946</v>
+        <v>80424</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,31 +2132,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2175,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695450</v>
+        <v>695359</v>
       </c>
       <c r="R16" t="n">
-        <v>7036585</v>
+        <v>7036639</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,8 +2203,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132034140</v>
+        <v>132034118</v>
       </c>
       <c r="B26" t="n">
-        <v>79319</v>
+        <v>58110</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,34 +3179,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695449</v>
+        <v>695490</v>
       </c>
       <c r="R26" t="n">
-        <v>7036505</v>
+        <v>7036280</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3236,9 +3244,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3265,7 +3283,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034141</v>
+        <v>132034140</v>
       </c>
       <c r="B27" t="n">
         <v>79319</v>
@@ -3300,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695346</v>
+        <v>695449</v>
       </c>
       <c r="R27" t="n">
-        <v>7036396</v>
+        <v>7036505</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3362,10 +3380,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034121</v>
+        <v>132034141</v>
       </c>
       <c r="B28" t="n">
-        <v>57946</v>
+        <v>79319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,42 +3391,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695332</v>
+        <v>695346</v>
       </c>
       <c r="R28" t="n">
-        <v>7036447</v>
+        <v>7036396</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,10 +3477,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034118</v>
+        <v>132034121</v>
       </c>
       <c r="B29" t="n">
-        <v>58110</v>
+        <v>57946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,21 +3488,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3500,7 +3510,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3510,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695490</v>
+        <v>695332</v>
       </c>
       <c r="R29" t="n">
-        <v>7036280</v>
+        <v>7036447</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,19 +3553,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132012306</v>
       </c>
       <c r="B2" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132007310</v>
       </c>
       <c r="B3" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132034144</v>
       </c>
       <c r="B4" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>132014040</v>
       </c>
       <c r="B5" t="n">
-        <v>80297</v>
+        <v>80305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,51 +1076,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132034131</v>
+        <v>132014573</v>
       </c>
       <c r="B6" t="n">
-        <v>80424</v>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695355</v>
+        <v>695342</v>
       </c>
       <c r="R6" t="n">
-        <v>7036639</v>
+        <v>7036654</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,34 +1155,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1195,7 +1176,7 @@
         <v>132034114</v>
       </c>
       <c r="B7" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,48 +1270,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132014573</v>
+        <v>132034131</v>
       </c>
       <c r="B8" t="n">
-        <v>91882</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695342</v>
+        <v>695355</v>
       </c>
       <c r="R8" t="n">
-        <v>7036654</v>
+        <v>7036639</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,18 +1352,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
         <v>132034129</v>
       </c>
       <c r="B9" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>132034128</v>
       </c>
       <c r="B10" t="n">
-        <v>56518</v>
+        <v>56522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>132034124</v>
       </c>
       <c r="B11" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>132034110</v>
       </c>
       <c r="B12" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034126</v>
+        <v>132034122</v>
       </c>
       <c r="B13" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695417</v>
+        <v>695347</v>
       </c>
       <c r="R13" t="n">
-        <v>7036333</v>
+        <v>7036357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034122</v>
+        <v>132034126</v>
       </c>
       <c r="B14" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695347</v>
+        <v>695417</v>
       </c>
       <c r="R14" t="n">
-        <v>7036357</v>
+        <v>7036333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132034120</v>
+        <v>132034130</v>
       </c>
       <c r="B15" t="n">
-        <v>57946</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,31 +2027,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2059,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695450</v>
+        <v>695359</v>
       </c>
       <c r="R15" t="n">
-        <v>7036585</v>
+        <v>7036639</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,8 +2098,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2121,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132034130</v>
+        <v>132034120</v>
       </c>
       <c r="B16" t="n">
-        <v>80424</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,26 +2143,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2159,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695359</v>
+        <v>695450</v>
       </c>
       <c r="R16" t="n">
-        <v>7036639</v>
+        <v>7036585</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,24 +2219,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2240,7 +2240,7 @@
         <v>132034132</v>
       </c>
       <c r="B17" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>132034125</v>
       </c>
       <c r="B18" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,52 +2463,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034139</v>
+        <v>132034113</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>91871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695472</v>
+        <v>695344</v>
       </c>
       <c r="R19" t="n">
-        <v>7036445</v>
+        <v>7036394</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,7 +2542,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2568,10 +2560,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034142</v>
+        <v>132034139</v>
       </c>
       <c r="B20" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2597,16 +2589,23 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695378</v>
+        <v>695472</v>
       </c>
       <c r="R20" t="n">
-        <v>7036337</v>
+        <v>7036445</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,6 +2646,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2665,32 +2665,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034113</v>
+        <v>132034142</v>
       </c>
       <c r="B21" t="n">
-        <v>91861</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695344</v>
+        <v>695378</v>
       </c>
       <c r="R21" t="n">
-        <v>7036394</v>
+        <v>7036337</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
         <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>132034137</v>
       </c>
       <c r="B23" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>132034115</v>
       </c>
       <c r="B24" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>132034117</v>
       </c>
       <c r="B25" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132034118</v>
+        <v>132034140</v>
       </c>
       <c r="B26" t="n">
-        <v>58110</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,42 +3179,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695490</v>
+        <v>695449</v>
       </c>
       <c r="R26" t="n">
-        <v>7036280</v>
+        <v>7036505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,19 +3236,9 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3283,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132034140</v>
+        <v>132034141</v>
       </c>
       <c r="B27" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695449</v>
+        <v>695346</v>
       </c>
       <c r="R27" t="n">
-        <v>7036505</v>
+        <v>7036396</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3380,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132034141</v>
+        <v>132034121</v>
       </c>
       <c r="B28" t="n">
-        <v>79319</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3391,34 +3373,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695346</v>
+        <v>695332</v>
       </c>
       <c r="R28" t="n">
-        <v>7036396</v>
+        <v>7036447</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132034121</v>
+        <v>132034118</v>
       </c>
       <c r="B29" t="n">
-        <v>57946</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3488,21 +3478,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3510,7 +3500,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3520,10 +3510,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>695332</v>
+        <v>695490</v>
       </c>
       <c r="R29" t="n">
-        <v>7036447</v>
+        <v>7036280</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,9 +3543,19 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3585,7 +3585,7 @@
         <v>132034127</v>
       </c>
       <c r="B30" t="n">
-        <v>56518</v>
+        <v>56522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>132034109</v>
       </c>
       <c r="B31" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132013817</v>
+        <v>132034116</v>
       </c>
       <c r="B32" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3787,37 +3787,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695302</v>
+        <v>695468</v>
       </c>
       <c r="R32" t="n">
-        <v>7036682</v>
+        <v>7036290</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,6 +3847,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3861,22 +3866,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132034116</v>
+        <v>132013817</v>
       </c>
       <c r="B33" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3884,37 +3889,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695468</v>
+        <v>695302</v>
       </c>
       <c r="R33" t="n">
-        <v>7036290</v>
+        <v>7036682</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3944,11 +3949,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3963,12 +3963,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
         <v>132013416</v>
       </c>
       <c r="B34" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>132014471</v>
       </c>
       <c r="B35" t="n">
-        <v>80297</v>
+        <v>80305</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4186,48 +4186,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132014637</v>
+        <v>132012907</v>
       </c>
       <c r="B36" t="n">
-        <v>80297</v>
+        <v>91871</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695362</v>
+        <v>695475</v>
       </c>
       <c r="R36" t="n">
-        <v>7036633</v>
+        <v>7036617</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4268,7 +4265,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4290,7 +4286,7 @@
         <v>132011688</v>
       </c>
       <c r="B37" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4384,45 +4380,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132012907</v>
+        <v>132014637</v>
       </c>
       <c r="B38" t="n">
-        <v>91861</v>
+        <v>80305</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695475</v>
+        <v>695362</v>
       </c>
       <c r="R38" t="n">
-        <v>7036617</v>
+        <v>7036633</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4463,6 +4462,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>132034138</v>
       </c>
       <c r="B39" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,32 +4587,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132034111</v>
+        <v>132034143</v>
       </c>
       <c r="B40" t="n">
-        <v>91861</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695315</v>
+        <v>695430</v>
       </c>
       <c r="R40" t="n">
-        <v>7036513</v>
+        <v>7036304</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4684,32 +4684,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132034143</v>
+        <v>132034111</v>
       </c>
       <c r="B41" t="n">
-        <v>79319</v>
+        <v>91871</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695430</v>
+        <v>695315</v>
       </c>
       <c r="R41" t="n">
-        <v>7036304</v>
+        <v>7036513</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,50 +4781,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132006284</v>
+        <v>132012332</v>
       </c>
       <c r="B42" t="n">
-        <v>57137</v>
+        <v>91908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695748</v>
+        <v>695536</v>
       </c>
       <c r="R42" t="n">
-        <v>7036138</v>
+        <v>7036574</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4883,45 +4878,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132012332</v>
+        <v>132006284</v>
       </c>
       <c r="B43" t="n">
-        <v>91898</v>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695536</v>
+        <v>695748</v>
       </c>
       <c r="R43" t="n">
-        <v>7036574</v>
+        <v>7036138</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4983,7 +4983,7 @@
         <v>132034119</v>
       </c>
       <c r="B44" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>132034112</v>
       </c>
       <c r="B45" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>132034133</v>
       </c>
       <c r="B46" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -1076,48 +1076,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132014573</v>
+        <v>132034131</v>
       </c>
       <c r="B6" t="n">
-        <v>91892</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695342</v>
+        <v>695355</v>
       </c>
       <c r="R6" t="n">
-        <v>7036654</v>
+        <v>7036639</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1155,66 +1158,82 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132034114</v>
+        <v>132014573</v>
       </c>
       <c r="B7" t="n">
-        <v>91908</v>
+        <v>91892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695307</v>
+        <v>695342</v>
       </c>
       <c r="R7" t="n">
-        <v>7036500</v>
+        <v>7036654</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,22 +1277,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034131</v>
+        <v>132034114</v>
       </c>
       <c r="B8" t="n">
-        <v>80432</v>
+        <v>91908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,37 +1300,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695355</v>
+        <v>695307</v>
       </c>
       <c r="R8" t="n">
-        <v>7036639</v>
+        <v>7036500</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,24 +1368,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2358,53 +2358,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034125</v>
+        <v>132034113</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>91871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695395</v>
+        <v>695344</v>
       </c>
       <c r="R18" t="n">
-        <v>7036336</v>
+        <v>7036394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,45 +2455,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034113</v>
+        <v>132034139</v>
       </c>
       <c r="B19" t="n">
-        <v>91871</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695344</v>
+        <v>695472</v>
       </c>
       <c r="R19" t="n">
-        <v>7036394</v>
+        <v>7036445</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,6 +2541,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2560,7 +2560,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034139</v>
+        <v>132034142</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2589,23 +2589,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695472</v>
+        <v>695378</v>
       </c>
       <c r="R20" t="n">
-        <v>7036445</v>
+        <v>7036337</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,7 +2639,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2665,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132034142</v>
+        <v>132034125</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,34 +2668,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695378</v>
+        <v>695395</v>
       </c>
       <c r="R21" t="n">
-        <v>7036337</v>
+        <v>7036336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4085,48 +4085,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132014471</v>
+        <v>132012907</v>
       </c>
       <c r="B35" t="n">
-        <v>80305</v>
+        <v>91871</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695346</v>
+        <v>695475</v>
       </c>
       <c r="R35" t="n">
-        <v>7036647</v>
+        <v>7036617</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4167,7 +4164,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4186,45 +4182,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132012907</v>
+        <v>132014471</v>
       </c>
       <c r="B36" t="n">
-        <v>91871</v>
+        <v>80305</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695475</v>
+        <v>695346</v>
       </c>
       <c r="R36" t="n">
-        <v>7036617</v>
+        <v>7036647</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4265,6 +4264,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4283,48 +4283,51 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132011688</v>
+        <v>132014637</v>
       </c>
       <c r="B37" t="n">
-        <v>91908</v>
+        <v>80305</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695558</v>
+        <v>695362</v>
       </c>
       <c r="R37" t="n">
-        <v>7036477</v>
+        <v>7036633</v>
       </c>
       <c r="S37" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4362,6 +4365,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4380,51 +4384,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132014637</v>
+        <v>132011688</v>
       </c>
       <c r="B38" t="n">
-        <v>80305</v>
+        <v>91908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695362</v>
+        <v>695558</v>
       </c>
       <c r="R38" t="n">
-        <v>7036633</v>
+        <v>7036477</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4462,7 +4463,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132012306</v>
       </c>
       <c r="B2" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>132014573</v>
       </c>
       <c r="B7" t="n">
-        <v>91892</v>
+        <v>91893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>132034114</v>
       </c>
       <c r="B8" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1709,45 +1709,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132034110</v>
+        <v>132034122</v>
       </c>
       <c r="B12" t="n">
-        <v>91871</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695453</v>
+        <v>695347</v>
       </c>
       <c r="R12" t="n">
-        <v>7036611</v>
+        <v>7036357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,7 +1814,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132034122</v>
+        <v>132034126</v>
       </c>
       <c r="B13" t="n">
         <v>57950</v>
@@ -1839,7 +1847,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1849,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695347</v>
+        <v>695417</v>
       </c>
       <c r="R13" t="n">
-        <v>7036357</v>
+        <v>7036333</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,53 +1919,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132034126</v>
+        <v>132034110</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695417</v>
+        <v>695453</v>
       </c>
       <c r="R14" t="n">
-        <v>7036333</v>
+        <v>7036611</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2358,45 +2358,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132034113</v>
+        <v>132034139</v>
       </c>
       <c r="B18" t="n">
-        <v>91871</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695344</v>
+        <v>695472</v>
       </c>
       <c r="R18" t="n">
-        <v>7036394</v>
+        <v>7036445</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,6 +2444,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2455,7 +2463,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132034139</v>
+        <v>132034142</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2484,23 +2492,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695472</v>
+        <v>695378</v>
       </c>
       <c r="R19" t="n">
-        <v>7036445</v>
+        <v>7036337</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,7 +2542,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2560,32 +2560,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132034142</v>
+        <v>132034113</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695378</v>
+        <v>695344</v>
       </c>
       <c r="R20" t="n">
-        <v>7036337</v>
+        <v>7036394</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
         <v>132012638</v>
       </c>
       <c r="B22" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>132034109</v>
       </c>
       <c r="B31" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>132012907</v>
       </c>
       <c r="B35" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,51 +4283,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132014637</v>
+        <v>132011688</v>
       </c>
       <c r="B37" t="n">
-        <v>80305</v>
+        <v>91909</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695362</v>
+        <v>695558</v>
       </c>
       <c r="R37" t="n">
-        <v>7036633</v>
+        <v>7036477</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4365,7 +4362,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4384,48 +4380,51 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132011688</v>
+        <v>132014637</v>
       </c>
       <c r="B38" t="n">
-        <v>91908</v>
+        <v>80305</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695558</v>
+        <v>695362</v>
       </c>
       <c r="R38" t="n">
-        <v>7036477</v>
+        <v>7036633</v>
       </c>
       <c r="S38" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4463,6 +4462,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132034138</v>
+        <v>132012332</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,40 +4492,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695488</v>
+        <v>695536</v>
       </c>
       <c r="R39" t="n">
-        <v>7036361</v>
+        <v>7036574</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4557,78 +4554,77 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hänglavs rikt område</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132034143</v>
+        <v>132006284</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hömyran, Ång</t>
+          <t>Hömyran, Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695430</v>
+        <v>695748</v>
       </c>
       <c r="R40" t="n">
-        <v>7036304</v>
+        <v>7036138</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4672,57 +4668,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132034111</v>
+        <v>132034138</v>
       </c>
       <c r="B41" t="n">
-        <v>91871</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695315</v>
+        <v>695488</v>
       </c>
       <c r="R41" t="n">
-        <v>7036513</v>
+        <v>7036361</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,12 +4756,18 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hänglavs rikt område</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4781,48 +4786,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132012332</v>
+        <v>132034111</v>
       </c>
       <c r="B42" t="n">
-        <v>91908</v>
+        <v>91872</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695536</v>
+        <v>695315</v>
       </c>
       <c r="R42" t="n">
-        <v>7036574</v>
+        <v>7036513</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4866,65 +4871,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132006284</v>
+        <v>132034143</v>
       </c>
       <c r="B43" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Ång</t>
+          <t>Hömyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695748</v>
+        <v>695430</v>
       </c>
       <c r="R43" t="n">
-        <v>7036138</v>
+        <v>7036304</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4968,12 +4968,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5106,7 +5106,7 @@
         <v>132034112</v>
       </c>
       <c r="B45" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132014040</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132014471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132014637</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132006760</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011688</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132012332</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034114</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132014573</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132012306</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132012638</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1751,6 +1806,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132012907</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034109</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1945,6 +2010,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034110</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034111</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2139,6 +2214,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034112</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,6 +2316,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034113</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013817</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034137</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2536,6 +2631,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034138</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2641,6 +2741,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034139</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2738,6 +2843,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034140</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2835,6 +2945,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034141</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2932,6 +3047,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034142</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3029,6 +3149,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034143</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3130,6 +3255,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034144</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3246,6 +3376,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034129</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3362,6 +3497,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034130</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3478,6 +3618,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034131</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3599,6 +3744,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034132</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3715,6 +3865,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034133</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3820,6 +3975,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034120</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3925,6 +4085,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034121</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4030,6 +4195,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034122</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4135,6 +4305,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034124</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4240,6 +4415,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034125</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4345,6 +4525,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034126</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4455,6 +4640,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013416</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4561,6 +4751,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034115</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4663,6 +4858,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034116</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4769,6 +4969,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034117</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4871,6 +5076,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132006284</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4973,6 +5183,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132007310</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5088,6 +5303,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034118</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5211,6 +5431,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034119</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5308,6 +5533,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034127</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5410,6 +5640,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034128</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5519,8 +5754,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132034106</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>